--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_4sep26_Fri.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_4sep26_Fri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45017183-4C3F-4EBF-92FC-C79C05BF9B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3A64B6-42F8-413E-991E-44F4C8D7C4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1 (2)" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$278</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$278</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet1 (2)'!$A$1:$N$278</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$L$14</definedName>
   </definedNames>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3100" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3127" uniqueCount="276">
   <si>
     <t>Date</t>
   </si>
@@ -860,6 +860,12 @@
   </si>
   <si>
     <t>S 10*1280 :04 SEP 2026 09:00:44 AM</t>
+  </si>
+  <si>
+    <t>GTD</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -919,7 +925,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -980,6 +986,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1019,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1175,30 +1187,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1502,7 +1506,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:N282"/>
+  <dimension ref="A1:O282"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.08984375" style="10" customWidth="1"/>
@@ -1519,7 +1523,7 @@
     <col min="14" max="16384" width="8.81640625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1559,8 +1563,11 @@
       <c r="M1" s="18" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O1" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -1593,11 +1600,11 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B2, $C$2:$C$797, C2, $D$2:$D$797, D2, $E$2:$E$797, E2) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N2:N33" si="0">IF(COUNTIFS( $B$2:$B$797, B2, $C$2:$C$797, C2, $D$2:$D$797, D2, $E$2:$E$797, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
@@ -1625,18 +1632,18 @@
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="53" t="s">
         <v>41</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B3, $C$2:$C$797, C3, $D$2:$D$797, D3, $E$2:$E$797, E3) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>62</v>
       </c>
@@ -1669,11 +1676,11 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B4, $C$2:$C$797, C4, $D$2:$D$797, D4, $E$2:$E$797, E4) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>62</v>
       </c>
@@ -1706,11 +1713,11 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B5, $C$2:$C$797, C5, $D$2:$D$797, D5, $E$2:$E$797, E5) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
@@ -1743,11 +1750,11 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B6, $C$2:$C$797, C6, $D$2:$D$797, D6, $E$2:$E$797, E6) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>62</v>
       </c>
@@ -1780,11 +1787,11 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B7, $C$2:$C$797, C7, $D$2:$D$797, D7, $E$2:$E$797, E7) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>62</v>
       </c>
@@ -1817,11 +1824,11 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B8, $C$2:$C$797, C8, $D$2:$D$797, D8, $E$2:$E$797, E8) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
@@ -1854,11 +1861,11 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B9, $C$2:$C$797, C9, $D$2:$D$797, D9, $E$2:$E$797, E9) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>62</v>
       </c>
@@ -1886,18 +1893,18 @@
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="55" t="s">
+      <c r="J10" s="53" t="s">
         <v>41</v>
       </c>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B10, $C$2:$C$797, C10, $D$2:$D$797, D10, $E$2:$E$797, E10) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
@@ -1930,11 +1937,11 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B11, $C$2:$C$797, C11, $D$2:$D$797, D11, $E$2:$E$797, E11) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
@@ -1967,11 +1974,11 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B12, $C$2:$C$797, C12, $D$2:$D$797, D12, $E$2:$E$797, E12) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2004,11 +2011,11 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B13, $C$2:$C$797, C13, $D$2:$D$797, D13, $E$2:$E$797, E13) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
@@ -2041,11 +2048,11 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B14, $C$2:$C$797, C14, $D$2:$D$797, D14, $E$2:$E$797, E14) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2078,11 +2085,11 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B15, $C$2:$C$797, C15, $D$2:$D$797, D15, $E$2:$E$797, E15) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2115,7 +2122,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B16, $C$2:$C$797, C16, $D$2:$D$797, D16, $E$2:$E$797, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2162,7 +2169,7 @@
         <v>540</v>
       </c>
       <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B17, $C$2:$C$797, C17, $D$2:$D$797, D17, $E$2:$E$797, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2201,7 +2208,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B18, $C$2:$C$797, C18, $D$2:$D$797, D18, $E$2:$E$797, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2238,7 +2245,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B19, $C$2:$C$797, C19, $D$2:$D$797, D19, $E$2:$E$797, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2277,7 +2284,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B20, $C$2:$C$797, C20, $D$2:$D$797, D20, $E$2:$E$797, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2314,7 +2321,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B21, $C$2:$C$797, C21, $D$2:$D$797, D21, $E$2:$E$797, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2351,7 +2358,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B22, $C$2:$C$797, C22, $D$2:$D$797, D22, $E$2:$E$797, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2388,7 +2395,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B23, $C$2:$C$797, C23, $D$2:$D$797, D23, $E$2:$E$797, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2425,7 +2432,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B24, $C$2:$C$797, C24, $D$2:$D$797, D24, $E$2:$E$797, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2462,7 +2469,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B25, $C$2:$C$797, C25, $D$2:$D$797, D25, $E$2:$E$797, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2501,7 +2508,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B26, $C$2:$C$797, C26, $D$2:$D$797, D26, $E$2:$E$797, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2538,7 +2545,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B27, $C$2:$C$797, C27, $D$2:$D$797, D27, $E$2:$E$797, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2575,7 +2582,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B28, $C$2:$C$797, C28, $D$2:$D$797, D28, $E$2:$E$797, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2607,7 +2614,7 @@
       <c r="I29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="59" t="s">
+      <c r="J29" s="55" t="s">
         <v>41</v>
       </c>
       <c r="K29" s="27" t="s">
@@ -2621,7 +2628,7 @@
         <v>442</v>
       </c>
       <c r="N29" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B29, $C$2:$C$797, C29, $D$2:$D$797, D29, $E$2:$E$797, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2658,7 +2665,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B30, $C$2:$C$797, C30, $D$2:$D$797, D30, $E$2:$E$797, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2705,7 +2712,7 @@
         <v>650</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B31, $C$2:$C$797, C31, $D$2:$D$797, D31, $E$2:$E$797, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2746,7 +2753,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B32, $C$2:$C$797, C32, $D$2:$D$797, D32, $E$2:$E$797, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2783,7 +2790,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B33, $C$2:$C$797, C33, $D$2:$D$797, D33, $E$2:$E$797, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2822,7 +2829,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B34, $C$2:$C$797, C34, $D$2:$D$797, D34, $E$2:$E$797, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N34:N65" si="1">IF(COUNTIFS( $B$2:$B$797, B34, $C$2:$C$797, C34, $D$2:$D$797, D34, $E$2:$E$797, E34) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -2859,7 +2866,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B35, $C$2:$C$797, C35, $D$2:$D$797, D35, $E$2:$E$797, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2896,7 +2903,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B36, $C$2:$C$797, C36, $D$2:$D$797, D36, $E$2:$E$797, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2935,7 +2942,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B37, $C$2:$C$797, C37, $D$2:$D$797, D37, $E$2:$E$797, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2974,7 +2981,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B38, $C$2:$C$797, C38, $D$2:$D$797, D38, $E$2:$E$797, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3011,7 +3018,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B39, $C$2:$C$797, C39, $D$2:$D$797, D39, $E$2:$E$797, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3050,7 +3057,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B40, $C$2:$C$797, C40, $D$2:$D$797, D40, $E$2:$E$797, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3089,7 +3096,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B41, $C$2:$C$797, C41, $D$2:$D$797, D41, $E$2:$E$797, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3128,7 +3135,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B42, $C$2:$C$797, C42, $D$2:$D$797, D42, $E$2:$E$797, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3165,7 +3172,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B43, $C$2:$C$797, C43, $D$2:$D$797, D43, $E$2:$E$797, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3202,7 +3209,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B44, $C$2:$C$797, C44, $D$2:$D$797, D44, $E$2:$E$797, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3241,7 +3248,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B45, $C$2:$C$797, C45, $D$2:$D$797, D45, $E$2:$E$797, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3287,7 +3294,7 @@
         <v>300</v>
       </c>
       <c r="N46" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B46, $C$2:$C$797, C46, $D$2:$D$797, D46, $E$2:$E$797, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3326,7 +3333,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B47, $C$2:$C$797, C47, $D$2:$D$797, D47, $E$2:$E$797, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3363,7 +3370,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B48, $C$2:$C$797, C48, $D$2:$D$797, D48, $E$2:$E$797, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3409,7 +3416,7 @@
         <v>300</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B49, $C$2:$C$797, C49, $D$2:$D$797, D49, $E$2:$E$797, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3446,7 +3453,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B50, $C$2:$C$797, C50, $D$2:$D$797, D50, $E$2:$E$797, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3492,7 +3499,7 @@
         <v>300</v>
       </c>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B51, $C$2:$C$797, C51, $D$2:$D$797, D51, $E$2:$E$797, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3538,7 +3545,7 @@
         <v>460</v>
       </c>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B52, $C$2:$C$797, C52, $D$2:$D$797, D52, $E$2:$E$797, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3575,7 +3582,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B53, $C$2:$C$797, C53, $D$2:$D$797, D53, $E$2:$E$797, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3612,7 +3619,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B54, $C$2:$C$797, C54, $D$2:$D$797, D54, $E$2:$E$797, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3658,7 +3665,7 @@
         <v>650</v>
       </c>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B55, $C$2:$C$797, C55, $D$2:$D$797, D55, $E$2:$E$797, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3697,7 +3704,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B56, $C$2:$C$797, C56, $D$2:$D$797, D56, $E$2:$E$797, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3734,7 +3741,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B57, $C$2:$C$797, C57, $D$2:$D$797, D57, $E$2:$E$797, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3766,14 +3773,14 @@
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="55" t="s">
+      <c r="J58" s="53" t="s">
         <v>41</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B58, $C$2:$C$797, C58, $D$2:$D$797, D58, $E$2:$E$797, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3810,7 +3817,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B59, $C$2:$C$797, C59, $D$2:$D$797, D59, $E$2:$E$797, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3847,7 +3854,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B60, $C$2:$C$797, C60, $D$2:$D$797, D60, $E$2:$E$797, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3884,7 +3891,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B61, $C$2:$C$797, C61, $D$2:$D$797, D61, $E$2:$E$797, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3916,14 +3923,14 @@
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="55" t="s">
+      <c r="J62" s="53" t="s">
         <v>55</v>
       </c>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B62, $C$2:$C$797, C62, $D$2:$D$797, D62, $E$2:$E$797, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3962,7 +3969,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B63, $C$2:$C$797, C63, $D$2:$D$797, D63, $E$2:$E$797, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4008,7 +4015,7 @@
         <v>222.75</v>
       </c>
       <c r="N64" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B64, $C$2:$C$797, C64, $D$2:$D$797, D64, $E$2:$E$797, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4045,7 +4052,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B65, $C$2:$C$797, C65, $D$2:$D$797, D65, $E$2:$E$797, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4082,7 +4089,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B66, $C$2:$C$797, C66, $D$2:$D$797, D66, $E$2:$E$797, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N97" si="2">IF(COUNTIFS( $B$2:$B$797, B66, $C$2:$C$797, C66, $D$2:$D$797, D66, $E$2:$E$797, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -4119,7 +4126,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B67, $C$2:$C$797, C67, $D$2:$D$797, D67, $E$2:$E$797, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4156,7 +4163,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B68, $C$2:$C$797, C68, $D$2:$D$797, D68, $E$2:$E$797, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4193,7 +4200,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B69, $C$2:$C$797, C69, $D$2:$D$797, D69, $E$2:$E$797, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4225,14 +4232,14 @@
       <c r="I70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J70" s="55" t="s">
+      <c r="J70" s="53" t="s">
         <v>55</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B70, $C$2:$C$797, C70, $D$2:$D$797, D70, $E$2:$E$797, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4269,7 +4276,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B71, $C$2:$C$797, C71, $D$2:$D$797, D71, $E$2:$E$797, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4308,7 +4315,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B72, $C$2:$C$797, C72, $D$2:$D$797, D72, $E$2:$E$797, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4345,7 +4352,7 @@
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B73, $C$2:$C$797, C73, $D$2:$D$797, D73, $E$2:$E$797, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4377,14 +4384,14 @@
       <c r="I74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J74" s="55" t="s">
+      <c r="J74" s="53" t="s">
         <v>41</v>
       </c>
       <c r="K74" s="17"/>
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B74, $C$2:$C$797, C74, $D$2:$D$797, D74, $E$2:$E$797, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4430,7 +4437,7 @@
         <v>500</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B75, $C$2:$C$797, C75, $D$2:$D$797, D75, $E$2:$E$797, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4467,7 +4474,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B76, $C$2:$C$797, C76, $D$2:$D$797, D76, $E$2:$E$797, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4513,7 +4520,7 @@
         <v>300</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B77, $C$2:$C$797, C77, $D$2:$D$797, D77, $E$2:$E$797, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4550,7 +4557,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B78, $C$2:$C$797, C78, $D$2:$D$797, D78, $E$2:$E$797, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4587,7 +4594,7 @@
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B79, $C$2:$C$797, C79, $D$2:$D$797, D79, $E$2:$E$797, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4633,7 +4640,7 @@
         <v>300</v>
       </c>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B80, $C$2:$C$797, C80, $D$2:$D$797, D80, $E$2:$E$797, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4670,7 +4677,7 @@
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B81, $C$2:$C$797, C81, $D$2:$D$797, D81, $E$2:$E$797, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4707,7 +4714,7 @@
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B82, $C$2:$C$797, C82, $D$2:$D$797, D82, $E$2:$E$797, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4744,7 +4751,7 @@
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B83, $C$2:$C$797, C83, $D$2:$D$797, D83, $E$2:$E$797, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4781,7 +4788,7 @@
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B84, $C$2:$C$797, C84, $D$2:$D$797, D84, $E$2:$E$797, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4818,7 +4825,7 @@
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B85, $C$2:$C$797, C85, $D$2:$D$797, D85, $E$2:$E$797, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4864,7 +4871,7 @@
         <v>300</v>
       </c>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B86, $C$2:$C$797, C86, $D$2:$D$797, D86, $E$2:$E$797, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4911,7 +4918,7 @@
         <v>525</v>
       </c>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B87, $C$2:$C$797, C87, $D$2:$D$797, D87, $E$2:$E$797, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4957,7 +4964,7 @@
         <v>300</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B88, $C$2:$C$797, C88, $D$2:$D$797, D88, $E$2:$E$797, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5003,7 +5010,7 @@
         <v>516</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B89, $C$2:$C$797, C89, $D$2:$D$797, D89, $E$2:$E$797, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5040,7 +5047,7 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B90, $C$2:$C$797, C90, $D$2:$D$797, D90, $E$2:$E$797, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5077,7 +5084,7 @@
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B91, $C$2:$C$797, C91, $D$2:$D$797, D91, $E$2:$E$797, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5123,7 +5130,7 @@
         <v>450</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B92, $C$2:$C$797, C92, $D$2:$D$797, D92, $E$2:$E$797, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5163,7 +5170,7 @@
         <v>3156</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B93, $C$2:$C$797, C93, $D$2:$D$797, D93, $E$2:$E$797, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5200,7 +5207,7 @@
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
       <c r="N94" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B94, $C$2:$C$797, C94, $D$2:$D$797, D94, $E$2:$E$797, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5246,7 +5253,7 @@
         <v>300</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B95, $C$2:$C$797, C95, $D$2:$D$797, D95, $E$2:$E$797, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5292,11 +5299,11 @@
         <v>620.99999999999636</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B96, $C$2:$C$797, C96, $D$2:$D$797, D96, $E$2:$E$797, E96) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -5338,11 +5345,11 @@
         <v>250</v>
       </c>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B97, $C$2:$C$797, C97, $D$2:$D$797, D97, $E$2:$E$797, E97) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -5370,18 +5377,18 @@
       <c r="I98" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J98" s="56" t="s">
+      <c r="J98" s="54" t="s">
         <v>118</v>
       </c>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B98, $C$2:$C$797, C98, $D$2:$D$797, D98, $E$2:$E$797, E98) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N98:N108" si="3">IF(COUNTIFS( $B$2:$B$797, B98, $C$2:$C$797, C98, $D$2:$D$797, D98, $E$2:$E$797, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="6" t="s">
         <v>62</v>
       </c>
@@ -5416,11 +5423,11 @@
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B99, $C$2:$C$797, C99, $D$2:$D$797, D99, $E$2:$E$797, E99) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -5448,18 +5455,18 @@
       <c r="I100" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="56" t="s">
+      <c r="J100" s="54" t="s">
         <v>41</v>
       </c>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
       <c r="N100" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B100, $C$2:$C$797, C100, $D$2:$D$797, D100, $E$2:$E$797, E100) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6" t="s">
         <v>62</v>
       </c>
@@ -5492,11 +5499,11 @@
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B101, $C$2:$C$797, C101, $D$2:$D$797, D101, $E$2:$E$797, E101) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5531,11 +5538,11 @@
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
       <c r="N102" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B102, $C$2:$C$797, C102, $D$2:$D$797, D102, $E$2:$E$797, E102) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="6" t="s">
         <v>62</v>
       </c>
@@ -5568,11 +5575,11 @@
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B103, $C$2:$C$797, C103, $D$2:$D$797, D103, $E$2:$E$797, E103) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3">
         <v>46252.6875</v>
       </c>
@@ -5607,11 +5614,11 @@
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B104, $C$2:$C$797, C104, $D$2:$D$797, D104, $E$2:$E$797, E104) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="6" t="s">
         <v>62</v>
       </c>
@@ -5646,11 +5653,11 @@
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B105, $C$2:$C$797, C105, $D$2:$D$797, D105, $E$2:$E$797, E105) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="36">
         <v>46268.375</v>
       </c>
@@ -5692,11 +5699,11 @@
         <v>200</v>
       </c>
       <c r="N106" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B106, $C$2:$C$797, C106, $D$2:$D$797, D106, $E$2:$E$797, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:15" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="36">
         <v>46269.375509259262</v>
       </c>
@@ -5738,11 +5745,11 @@
         <v>300</v>
       </c>
       <c r="N107" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B107, $C$2:$C$797, C107, $D$2:$D$797, D107, $E$2:$E$797, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
         <v>46269.375509259262</v>
       </c>
@@ -5785,11 +5792,11 @@
         <v>290</v>
       </c>
       <c r="N108" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B108, $C$2:$C$797, C108, $D$2:$D$797, D108, $E$2:$E$797, E108) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -5824,8 +5831,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B109, $C$2:$C$797, C109, $D$2:$D$797, D109, $E$2:$E$797, E109) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" s="25" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O109" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" s="25" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3">
         <v>46266.375</v>
       </c>
@@ -5870,8 +5880,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B110, $C$2:$C$797, C110, $D$2:$D$797, D110, $E$2:$E$797, E110) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O110" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -5916,8 +5929,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B111, $C$2:$C$797, C111, $D$2:$D$797, D111, $E$2:$E$797, E111) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O111" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>46265.392361111109</v>
       </c>
@@ -5962,8 +5978,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B112, $C$2:$C$797, C112, $D$2:$D$797, D112, $E$2:$E$797, E112) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O112" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3">
         <v>46269.542858796296</v>
       </c>
@@ -6009,7 +6028,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -6054,8 +6073,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B114, $C$2:$C$797, C114, $D$2:$D$797, D114, $E$2:$E$797, E114) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O114" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6100,8 +6122,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B115, $C$2:$C$797, C115, $D$2:$D$797, D115, $E$2:$E$797, E115) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O115" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6146,8 +6171,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B116, $C$2:$C$797, C116, $D$2:$D$797, D116, $E$2:$E$797, E116) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O116" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46266.375</v>
       </c>
@@ -6193,7 +6221,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="118" spans="1:14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="11">
         <v>46252.6875</v>
       </c>
@@ -6231,8 +6259,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B118, $C$2:$C$797, C118, $D$2:$D$797, D118, $E$2:$E$797, E118) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O118" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3">
         <v>46265.466666666667</v>
       </c>
@@ -6277,8 +6308,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B119, $C$2:$C$797, C119, $D$2:$D$797, D119, $E$2:$E$797, E119) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O119" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3">
         <v>46261.375</v>
       </c>
@@ -6324,7 +6358,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="121" spans="1:14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3">
         <v>46269.614710648151</v>
       </c>
@@ -6369,8 +6403,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B121, $C$2:$C$797, C121, $D$2:$D$797, D121, $E$2:$E$797, E121) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O121" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -6416,7 +6453,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="123" spans="1:14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -6462,7 +6499,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="124" spans="1:14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -6507,8 +6544,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B124, $C$2:$C$797, C124, $D$2:$D$797, D124, $E$2:$E$797, E124) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O124" s="58" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3">
         <v>46267.425694444442</v>
       </c>
@@ -6553,8 +6593,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B125, $C$2:$C$797, C125, $D$2:$D$797, D125, $E$2:$E$797, E125) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O125" s="58" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3">
         <v>46268.375</v>
       </c>
@@ -6599,8 +6642,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B126, $C$2:$C$797, C126, $D$2:$D$797, D126, $E$2:$E$797, E126) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O126" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3">
         <v>46267.375</v>
       </c>
@@ -6645,8 +6691,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B127, $C$2:$C$797, C127, $D$2:$D$797, D127, $E$2:$E$797, E127) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O127" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3">
         <v>46269.411423611113</v>
       </c>
@@ -6691,8 +6740,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B128, $C$2:$C$797, C128, $D$2:$D$797, D128, $E$2:$E$797, E128) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O128" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3">
         <v>46267.375</v>
       </c>
@@ -6737,8 +6789,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B129, $C$2:$C$797, C129, $D$2:$D$797, D129, $E$2:$E$797, E129) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O129" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6772,7 +6827,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="131" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6818,7 +6873,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="132" spans="1:14" s="19" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:15" s="19" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="36">
         <v>46262.375</v>
       </c>
@@ -6863,8 +6918,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B132, $C$2:$C$797, C132, $D$2:$D$797, D132, $E$2:$E$797, E132) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" s="26" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O132" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" s="26" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -6909,8 +6967,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B133, $C$2:$C$797, C133, $D$2:$D$797, D133, $E$2:$E$797, E133) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O133" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6943,8 +7004,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B134, $C$2:$C$797, C134, $D$2:$D$797, D134, $E$2:$E$797, E134) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O134" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46266.375</v>
       </c>
@@ -6990,7 +7054,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="36">
         <v>46267.375</v>
       </c>
@@ -7035,8 +7099,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B136, $C$2:$C$797, C136, $D$2:$D$797, D136, $E$2:$E$797, E136) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O136" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="36">
         <v>46267.375</v>
       </c>
@@ -7081,8 +7148,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B137, $C$2:$C$797, C137, $D$2:$D$797, D137, $E$2:$E$797, E137) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O137" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -7128,7 +7198,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="139" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3">
         <v>46267.375</v>
       </c>
@@ -7174,7 +7244,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="140" spans="1:14" s="25" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:15" s="25" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -7211,7 +7281,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3">
         <v>46262.375</v>
       </c>
@@ -7257,7 +7327,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -7303,7 +7373,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="143" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7331,7 +7401,7 @@
       <c r="I143" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J143" s="58" t="s">
+      <c r="J143" s="17" t="s">
         <v>117</v>
       </c>
       <c r="N143" s="10" t="str">
@@ -7339,7 +7409,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3">
         <v>46266.375</v>
       </c>
@@ -7384,8 +7454,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B144, $C$2:$C$797, C144, $D$2:$D$797, D144, $E$2:$E$797, E144) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" s="26" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O144" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" s="26" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="36">
         <v>46267.461111111108</v>
       </c>
@@ -7431,7 +7504,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="36">
         <v>46267.38958333333</v>
       </c>
@@ -7477,7 +7550,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="147" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="3">
         <v>46269.643587962964</v>
       </c>
@@ -7522,8 +7595,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B147, $C$2:$C$797, C147, $D$2:$D$797, D147, $E$2:$E$797, E147) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O147" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3">
         <v>46262.375</v>
       </c>
@@ -7569,7 +7645,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="149" spans="1:14" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:15" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -7614,8 +7690,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B149, $C$2:$C$797, C149, $D$2:$D$797, D149, $E$2:$E$797, E149) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O149" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3">
         <v>46262.375</v>
       </c>
@@ -7661,7 +7740,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="151" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -7689,7 +7768,7 @@
       <c r="I151" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J151" s="58" t="s">
+      <c r="J151" s="17" t="s">
         <v>117</v>
       </c>
       <c r="K151" s="17" t="s">
@@ -7702,7 +7781,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="152" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3">
         <v>46267.375</v>
       </c>
@@ -7748,7 +7827,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="153" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -7794,7 +7873,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="154" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46266.375</v>
       </c>
@@ -7840,7 +7919,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="155" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -7874,7 +7953,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="156" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -7902,7 +7981,7 @@
       <c r="I156" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J156" s="54" t="s">
+      <c r="J156" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K156" s="18" t="s">
@@ -7919,8 +7998,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B156, $C$2:$C$797, C156, $D$2:$D$797, D156, $E$2:$E$797, E156) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O156" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3">
         <v>46261.375</v>
       </c>
@@ -7966,7 +8048,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="11">
         <v>46252.6875</v>
       </c>
@@ -7994,7 +8076,7 @@
       <c r="I158" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J158" s="53" t="s">
+      <c r="J158" s="40" t="s">
         <v>156</v>
       </c>
       <c r="N158" s="10" t="str">
@@ -8002,7 +8084,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="159" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="11">
         <v>46252.6875</v>
       </c>
@@ -8038,7 +8120,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3">
         <v>46268.375</v>
       </c>
@@ -8066,7 +8148,7 @@
       <c r="I160" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J160" s="54" t="s">
+      <c r="J160" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K160" s="18" t="s">
@@ -8112,7 +8194,7 @@
       <c r="I161" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J161" s="54" t="s">
+      <c r="J161" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K161" s="18" t="s">
@@ -8158,7 +8240,7 @@
       <c r="I162" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J162" s="53" t="s">
+      <c r="J162" s="40" t="s">
         <v>117</v>
       </c>
       <c r="N162" s="10" t="str">
@@ -8194,7 +8276,7 @@
       <c r="I163" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J163" s="54" t="s">
+      <c r="J163" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K163" s="18" t="s">
@@ -8240,7 +8322,7 @@
       <c r="I164" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J164" s="53"/>
+      <c r="J164" s="40"/>
       <c r="N164" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B164, $C$2:$C$797, C164, $D$2:$D$797, D164, $E$2:$E$797, E164) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -8458,7 +8540,7 @@
       <c r="I169" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J169" s="53"/>
+      <c r="J169" s="40"/>
       <c r="N169" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B169, $C$2:$C$797, C169, $D$2:$D$797, D169, $E$2:$E$797, E169) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -8538,7 +8620,7 @@
       <c r="I171" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J171" s="54" t="s">
+      <c r="J171" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K171" s="18" t="s">
@@ -8584,7 +8666,7 @@
       <c r="I172" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J172" s="54" t="s">
+      <c r="J172" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K172" s="18" t="s">
@@ -8630,7 +8712,7 @@
       <c r="I173" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J173" s="57" t="s">
+      <c r="J173" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K173" s="18" t="s">
@@ -8676,7 +8758,7 @@
       <c r="I174" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J174" s="54" t="s">
+      <c r="J174" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K174" s="18" t="s">
@@ -8722,7 +8804,7 @@
       <c r="I175" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J175" s="53"/>
+      <c r="J175" s="40"/>
       <c r="N175" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B175, $C$2:$C$797, C175, $D$2:$D$797, D175, $E$2:$E$797, E175) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -8756,7 +8838,7 @@
       <c r="I176" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J176" s="54" t="s">
+      <c r="J176" s="18" t="s">
         <v>118</v>
       </c>
       <c r="N176" s="10" t="str">
@@ -8792,7 +8874,7 @@
       <c r="I177" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J177" s="53"/>
+      <c r="J177" s="40"/>
       <c r="N177" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B177, $C$2:$C$797, C177, $D$2:$D$797, D177, $E$2:$E$797, E177) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -8826,7 +8908,7 @@
       <c r="I178" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J178" s="54" t="s">
+      <c r="J178" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K178" s="18" t="s">
@@ -8872,7 +8954,7 @@
       <c r="I179" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J179" s="53" t="s">
+      <c r="J179" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N179" s="10" t="str">
@@ -8908,7 +8990,7 @@
       <c r="I180" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J180" s="54" t="s">
+      <c r="J180" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K180" s="18" t="s">
@@ -9000,8 +9082,8 @@
       <c r="I182" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J182" s="53" t="s">
-        <v>41</v>
+      <c r="J182" s="40" t="s">
+        <v>117</v>
       </c>
       <c r="N182" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B182, $C$2:$C$797, C182, $D$2:$D$797, D182, $E$2:$E$797, E182) &gt; 1, "Duplicate", "Unique")</f>
@@ -9036,8 +9118,8 @@
       <c r="I183" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J183" s="54" t="s">
-        <v>41</v>
+      <c r="J183" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="K183" s="18" t="s">
         <v>205</v>
@@ -9082,7 +9164,7 @@
       <c r="I184" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J184" s="54" t="s">
+      <c r="J184" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K184" s="18" t="s">
@@ -9128,7 +9210,7 @@
       <c r="I185" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J185" s="54" t="s">
+      <c r="J185" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K185" s="18" t="s">
@@ -9174,7 +9256,7 @@
       <c r="I186" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J186" s="54" t="s">
+      <c r="J186" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K186" s="18" t="s">
@@ -9220,7 +9302,7 @@
       <c r="I187" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J187" s="53" t="s">
+      <c r="J187" s="40" t="s">
         <v>117</v>
       </c>
       <c r="N187" s="10" t="str">
@@ -9256,7 +9338,7 @@
       <c r="I188" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J188" s="54" t="s">
+      <c r="J188" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K188" s="18" t="s">
@@ -9302,7 +9384,7 @@
       <c r="I189" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J189" s="54" t="s">
+      <c r="J189" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K189" s="18" t="s">
@@ -9348,7 +9430,7 @@
       <c r="I190" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J190" s="54" t="s">
+      <c r="J190" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K190" s="18" t="s">
@@ -9394,7 +9476,7 @@
       <c r="I191" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J191" s="54" t="s">
+      <c r="J191" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K191" s="18" t="s">
@@ -9440,7 +9522,7 @@
       <c r="I192" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J192" s="53" t="s">
+      <c r="J192" s="40" t="s">
         <v>201</v>
       </c>
       <c r="N192" s="10" t="str">
@@ -9476,7 +9558,7 @@
       <c r="I193" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J193" s="53"/>
+      <c r="J193" s="40"/>
       <c r="N193" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B193, $C$2:$C$797, C193, $D$2:$D$797, D193, $E$2:$E$797, E193) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -9510,7 +9592,7 @@
       <c r="I194" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J194" s="54" t="s">
+      <c r="J194" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K194" s="18" t="s">
@@ -9556,7 +9638,7 @@
       <c r="I195" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J195" s="53" t="s">
+      <c r="J195" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K195" s="18" t="s">
@@ -9595,7 +9677,7 @@
       <c r="I196" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J196" s="53"/>
+      <c r="J196" s="40"/>
       <c r="K196" s="18"/>
       <c r="L196" s="18"/>
       <c r="M196" s="18"/>
@@ -9632,7 +9714,7 @@
       <c r="I197" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J197" s="57" t="s">
+      <c r="J197" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K197" s="33" t="s">
@@ -9678,7 +9760,7 @@
       <c r="I198" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J198" s="57" t="s">
+      <c r="J198" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K198" s="33" t="s">
@@ -9724,7 +9806,7 @@
       <c r="I199" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J199" s="57" t="s">
+      <c r="J199" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K199" s="33" t="s">
@@ -9770,7 +9852,7 @@
       <c r="I200" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J200" s="57" t="s">
+      <c r="J200" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K200" s="33" t="s">
@@ -9816,7 +9898,7 @@
       <c r="I201" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J201" s="53"/>
+      <c r="J201" s="40"/>
       <c r="N201" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B201, $C$2:$C$797, C201, $D$2:$D$797, D201, $E$2:$E$797, E201) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -9850,7 +9932,7 @@
       <c r="I202" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J202" s="53"/>
+      <c r="J202" s="40"/>
       <c r="N202" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B202, $C$2:$C$797, C202, $D$2:$D$797, D202, $E$2:$E$797, E202) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -9884,7 +9966,7 @@
       <c r="I203" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J203" s="53" t="s">
+      <c r="J203" s="40" t="s">
         <v>117</v>
       </c>
       <c r="N203" s="10" t="str">
@@ -9920,7 +10002,7 @@
       <c r="I204" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J204" s="53" t="s">
+      <c r="J204" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N204" s="10" t="str">
@@ -9956,7 +10038,7 @@
       <c r="I205" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J205" s="54" t="s">
+      <c r="J205" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K205" s="18" t="s">
@@ -10002,7 +10084,7 @@
       <c r="I206" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J206" s="53" t="s">
+      <c r="J206" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N206" s="10" t="str">
@@ -10038,7 +10120,7 @@
       <c r="I207" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J207" s="53" t="s">
+      <c r="J207" s="40" t="s">
         <v>55</v>
       </c>
       <c r="N207" s="10" t="str">
@@ -10074,15 +10156,15 @@
       <c r="I208" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J208" s="53" t="s">
-        <v>41</v>
+      <c r="J208" s="40" t="s">
+        <v>117</v>
       </c>
       <c r="N208" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B208, $C$2:$C$797, C208, $D$2:$D$797, D208, $E$2:$E$797, E208) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="209" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="8" t="s">
         <v>62</v>
       </c>
@@ -10110,7 +10192,7 @@
       <c r="I209" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J209" s="53" t="s">
+      <c r="J209" s="40" t="s">
         <v>117</v>
       </c>
       <c r="N209" s="10" t="str">
@@ -10118,7 +10200,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="210" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -10146,7 +10228,7 @@
       <c r="I210" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J210" s="58" t="s">
+      <c r="J210" s="17" t="s">
         <v>117</v>
       </c>
       <c r="N210" s="10" t="str">
@@ -10154,7 +10236,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="211" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10182,7 +10264,7 @@
       <c r="I211" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J211" s="54" t="s">
+      <c r="J211" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K211" s="18" t="s">
@@ -10200,7 +10282,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="212" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>46253.375</v>
       </c>
@@ -10228,7 +10310,7 @@
       <c r="I212" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J212" s="53" t="s">
+      <c r="J212" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K212" s="18" t="s">
@@ -10239,7 +10321,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="213" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -10267,7 +10349,7 @@
       <c r="I213" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J213" s="54" t="s">
+      <c r="J213" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K213" s="18" t="s">
@@ -10284,8 +10366,11 @@
         <f>IF(COUNTIFS( $B$2:$B$797, B213, $C$2:$C$797, C213, $D$2:$D$797, D213, $E$2:$E$797, E213) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O213" s="57" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="3">
         <v>46261.375</v>
       </c>
@@ -10313,7 +10398,7 @@
       <c r="I214" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J214" s="54" t="s">
+      <c r="J214" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K214" s="18" t="s">
@@ -10331,7 +10416,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="215" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -10377,7 +10462,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="216" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3">
         <v>46266.375</v>
       </c>
@@ -10405,7 +10490,7 @@
       <c r="I216" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J216" s="54" t="s">
+      <c r="J216" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K216" s="18" t="s">
@@ -10423,7 +10508,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="217" spans="1:14" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:15" s="35" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="3">
         <v>46259.375</v>
       </c>
@@ -10451,7 +10536,7 @@
       <c r="I217" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J217" s="53" t="s">
+      <c r="J217" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K217" s="18" t="s">
@@ -10469,7 +10554,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="218" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="3">
         <v>46260.375</v>
       </c>
@@ -10497,7 +10582,7 @@
       <c r="I218" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J218" s="54" t="s">
+      <c r="J218" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K218" s="18" t="s">
@@ -10515,7 +10600,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="219" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10543,13 +10628,13 @@
       <c r="I219" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J219" s="53"/>
+      <c r="J219" s="40"/>
       <c r="N219" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B219, $C$2:$C$797, C219, $D$2:$D$797, D219, $E$2:$E$797, E219) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="220" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="8" t="s">
         <v>62</v>
       </c>
@@ -10577,13 +10662,13 @@
       <c r="I220" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J220" s="53"/>
+      <c r="J220" s="40"/>
       <c r="N220" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B220, $C$2:$C$797, C220, $D$2:$D$797, D220, $E$2:$E$797, E220) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="221" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="8" t="s">
         <v>62</v>
       </c>
@@ -10611,13 +10696,13 @@
       <c r="I221" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J221" s="53"/>
+      <c r="J221" s="40"/>
       <c r="N221" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B221, $C$2:$C$797, C221, $D$2:$D$797, D221, $E$2:$E$797, E221) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="222" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="8" t="s">
         <v>62</v>
       </c>
@@ -10645,7 +10730,7 @@
       <c r="I222" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J222" s="53" t="s">
+      <c r="J222" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N222" s="10" t="str">
@@ -10653,7 +10738,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="223" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="3">
         <v>46260.375</v>
       </c>
@@ -10681,7 +10766,7 @@
       <c r="I223" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J223" s="54" t="s">
+      <c r="J223" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K223" s="18" t="s">
@@ -10699,7 +10784,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="224" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="8" t="s">
         <v>62</v>
       </c>
@@ -10727,7 +10812,7 @@
       <c r="I224" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J224" s="53" t="s">
+      <c r="J224" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N224" s="10" t="str">
@@ -10763,7 +10848,7 @@
       <c r="I225" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J225" s="53"/>
+      <c r="J225" s="40"/>
       <c r="K225" s="18"/>
       <c r="L225" s="18"/>
       <c r="M225" s="18"/>
@@ -10800,7 +10885,7 @@
       <c r="I226" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J226" s="60" t="s">
+      <c r="J226" s="56" t="s">
         <v>55</v>
       </c>
       <c r="N226" s="10" t="str">
@@ -10836,7 +10921,7 @@
       <c r="I227" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J227" s="53" t="s">
+      <c r="J227" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N227" s="10" t="str">
@@ -10872,7 +10957,7 @@
       <c r="I228" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J228" s="53" t="s">
+      <c r="J228" s="40" t="s">
         <v>117</v>
       </c>
       <c r="N228" s="10" t="str">
@@ -10908,7 +10993,7 @@
       <c r="I229" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J229" s="53"/>
+      <c r="J229" s="40"/>
       <c r="N229" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B229, $C$2:$C$797, C229, $D$2:$D$797, D229, $E$2:$E$797, E229) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -10942,7 +11027,7 @@
       <c r="I230" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J230" s="53" t="s">
+      <c r="J230" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K230" s="18"/>
@@ -10981,7 +11066,7 @@
       <c r="I231" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J231" s="53" t="s">
+      <c r="J231" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K231" s="18"/>
@@ -11066,8 +11151,8 @@
       <c r="I233" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J233" s="54" t="s">
-        <v>41</v>
+      <c r="J233" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="K233" s="18" t="s">
         <v>210</v>
@@ -11112,7 +11197,7 @@
       <c r="I234" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J234" s="53" t="s">
+      <c r="J234" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N234" s="10" t="str">
@@ -11148,7 +11233,7 @@
       <c r="I235" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J235" s="53"/>
+      <c r="J235" s="40"/>
       <c r="N235" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B235, $C$2:$C$797, C235, $D$2:$D$797, D235, $E$2:$E$797, E235) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11182,7 +11267,7 @@
       <c r="I236" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J236" s="53" t="s">
+      <c r="J236" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K236" s="18" t="s">
@@ -11221,7 +11306,7 @@
       <c r="I237" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J237" s="54" t="s">
+      <c r="J237" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K237" s="18" t="s">
@@ -11267,7 +11352,7 @@
       <c r="I238" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J238" s="54" t="s">
+      <c r="J238" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K238" s="18" t="s">
@@ -11313,7 +11398,7 @@
       <c r="I239" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J239" s="53"/>
+      <c r="J239" s="40"/>
       <c r="N239" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B239, $C$2:$C$797, C239, $D$2:$D$797, D239, $E$2:$E$797, E239) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11347,7 +11432,7 @@
       <c r="I240" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J240" s="53" t="s">
+      <c r="J240" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N240" s="10" t="str">
@@ -11383,7 +11468,7 @@
       <c r="I241" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J241" s="53"/>
+      <c r="J241" s="40"/>
       <c r="N241" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B241, $C$2:$C$797, C241, $D$2:$D$797, D241, $E$2:$E$797, E241) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11417,7 +11502,7 @@
       <c r="I242" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J242" s="54" t="s">
+      <c r="J242" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K242" s="18" t="s">
@@ -11456,7 +11541,7 @@
       <c r="I243" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J243" s="53"/>
+      <c r="J243" s="40"/>
       <c r="N243" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B243, $C$2:$C$797, C243, $D$2:$D$797, D243, $E$2:$E$797, E243) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11490,7 +11575,7 @@
       <c r="I244" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J244" s="53" t="s">
+      <c r="J244" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N244" s="10" t="str">
@@ -11526,7 +11611,7 @@
       <c r="I245" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J245" s="53"/>
+      <c r="J245" s="40"/>
       <c r="N245" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B245, $C$2:$C$797, C245, $D$2:$D$797, D245, $E$2:$E$797, E245) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11560,7 +11645,7 @@
       <c r="I246" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J246" s="53"/>
+      <c r="J246" s="40"/>
       <c r="N246" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B246, $C$2:$C$797, C246, $D$2:$D$797, D246, $E$2:$E$797, E246) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11594,7 +11679,7 @@
       <c r="I247" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J247" s="53" t="s">
+      <c r="J247" s="40" t="s">
         <v>117</v>
       </c>
       <c r="N247" s="10" t="str">
@@ -11630,7 +11715,7 @@
       <c r="I248" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J248" s="53"/>
+      <c r="J248" s="40"/>
       <c r="N248" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B248, $C$2:$C$797, C248, $D$2:$D$797, D248, $E$2:$E$797, E248) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11664,7 +11749,7 @@
       <c r="I249" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J249" s="54" t="s">
+      <c r="J249" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K249" s="18" t="s">
@@ -11710,7 +11795,7 @@
       <c r="I250" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J250" s="53" t="s">
+      <c r="J250" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N250" s="10" t="str">
@@ -11746,7 +11831,7 @@
       <c r="I251" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J251" s="53"/>
+      <c r="J251" s="40"/>
       <c r="N251" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B251, $C$2:$C$797, C251, $D$2:$D$797, D251, $E$2:$E$797, E251) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11780,7 +11865,7 @@
       <c r="I252" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J252" s="53"/>
+      <c r="J252" s="40"/>
       <c r="N252" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B252, $C$2:$C$797, C252, $D$2:$D$797, D252, $E$2:$E$797, E252) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11814,7 +11899,7 @@
       <c r="I253" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J253" s="53" t="s">
+      <c r="J253" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K253" s="18"/>
@@ -11853,7 +11938,7 @@
       <c r="I254" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J254" s="54" t="s">
+      <c r="J254" s="18" t="s">
         <v>55</v>
       </c>
       <c r="K254" s="18" t="s">
@@ -11899,7 +11984,7 @@
       <c r="I255" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J255" s="53" t="s">
+      <c r="J255" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N255" s="10" t="str">
@@ -11935,7 +12020,7 @@
       <c r="I256" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J256" s="53"/>
+      <c r="J256" s="40"/>
       <c r="N256" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B256, $C$2:$C$797, C256, $D$2:$D$797, D256, $E$2:$E$797, E256) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -11969,7 +12054,7 @@
       <c r="I257" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J257" s="53"/>
+      <c r="J257" s="40"/>
       <c r="N257" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B257, $C$2:$C$797, C257, $D$2:$D$797, D257, $E$2:$E$797, E257) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12003,7 +12088,7 @@
       <c r="I258" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J258" s="53"/>
+      <c r="J258" s="40"/>
       <c r="K258" s="18"/>
       <c r="L258" s="18"/>
       <c r="M258" s="18"/>
@@ -12040,7 +12125,7 @@
       <c r="I259" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J259" s="53"/>
+      <c r="J259" s="40"/>
       <c r="N259" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B259, $C$2:$C$797, C259, $D$2:$D$797, D259, $E$2:$E$797, E259) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12074,7 +12159,7 @@
       <c r="I260" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J260" s="53"/>
+      <c r="J260" s="40"/>
       <c r="N260" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B260, $C$2:$C$797, C260, $D$2:$D$797, D260, $E$2:$E$797, E260) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12108,7 +12193,7 @@
       <c r="I261" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J261" s="53"/>
+      <c r="J261" s="40"/>
       <c r="N261" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B261, $C$2:$C$797, C261, $D$2:$D$797, D261, $E$2:$E$797, E261) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12142,7 +12227,7 @@
       <c r="I262" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J262" s="53"/>
+      <c r="J262" s="40"/>
       <c r="N262" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B262, $C$2:$C$797, C262, $D$2:$D$797, D262, $E$2:$E$797, E262) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12176,7 +12261,7 @@
       <c r="I263" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J263" s="53"/>
+      <c r="J263" s="40"/>
       <c r="N263" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B263, $C$2:$C$797, C263, $D$2:$D$797, D263, $E$2:$E$797, E263) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12210,7 +12295,7 @@
       <c r="I264" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J264" s="53" t="s">
+      <c r="J264" s="40" t="s">
         <v>55</v>
       </c>
       <c r="N264" s="10" t="str">
@@ -12246,7 +12331,7 @@
       <c r="I265" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J265" s="53"/>
+      <c r="J265" s="40"/>
       <c r="N265" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B265, $C$2:$C$797, C265, $D$2:$D$797, D265, $E$2:$E$797, E265) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12280,7 +12365,7 @@
       <c r="I266" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J266" s="53"/>
+      <c r="J266" s="40"/>
       <c r="N266" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B266, $C$2:$C$797, C266, $D$2:$D$797, D266, $E$2:$E$797, E266) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12314,7 +12399,7 @@
       <c r="I267" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J267" s="54" t="s">
+      <c r="J267" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K267" s="18" t="s">
@@ -12360,7 +12445,7 @@
       <c r="I268" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J268" s="53"/>
+      <c r="J268" s="40"/>
       <c r="N268" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B268, $C$2:$C$797, C268, $D$2:$D$797, D268, $E$2:$E$797, E268) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12394,7 +12479,7 @@
       <c r="I269" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J269" s="53" t="s">
+      <c r="J269" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N269" s="10" t="str">
@@ -12430,7 +12515,7 @@
       <c r="I270" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J270" s="53"/>
+      <c r="J270" s="40"/>
       <c r="N270" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B270, $C$2:$C$797, C270, $D$2:$D$797, D270, $E$2:$E$797, E270) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12464,7 +12549,7 @@
       <c r="I271" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J271" s="53" t="s">
+      <c r="J271" s="40" t="s">
         <v>118</v>
       </c>
       <c r="K271" s="18" t="s">
@@ -12510,7 +12595,7 @@
       <c r="I272" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J272" s="53"/>
+      <c r="J272" s="40"/>
       <c r="N272" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B272, $C$2:$C$797, C272, $D$2:$D$797, D272, $E$2:$E$797, E272) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12544,7 +12629,7 @@
       <c r="I273" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J273" s="53"/>
+      <c r="J273" s="40"/>
       <c r="N273" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$797, B273, $C$2:$C$797, C273, $D$2:$D$797, D273, $E$2:$E$797, E273) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -12578,7 +12663,7 @@
       <c r="I274" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J274" s="53" t="s">
+      <c r="J274" s="40" t="s">
         <v>118</v>
       </c>
       <c r="N274" s="10" t="str">
@@ -12614,9 +12699,9 @@
       <c r="I275" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J275" s="53"/>
+      <c r="J275" s="40"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B275, $C$2:$C$797, C275, $D$2:$D$797, D275, $E$2:$E$797, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N278" si="4">IF(COUNTIFS( $B$2:$B$797, B275, $C$2:$C$797, C275, $D$2:$D$797, D275, $E$2:$E$797, E275) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12648,9 +12733,9 @@
       <c r="I276" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J276" s="53"/>
+      <c r="J276" s="40"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B276, $C$2:$C$797, C276, $D$2:$D$797, D276, $E$2:$E$797, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12682,12 +12767,12 @@
       <c r="I277" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J277" s="53"/>
+      <c r="J277" s="40"/>
       <c r="K277" s="18"/>
       <c r="L277" s="18"/>
       <c r="M277" s="18"/>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B277, $C$2:$C$797, C277, $D$2:$D$797, D277, $E$2:$E$797, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12719,9 +12804,9 @@
       <c r="I278" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J278" s="53"/>
+      <c r="J278" s="40"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B278, $C$2:$C$797, C278, $D$2:$D$797, D278, $E$2:$E$797, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12743,14 +12828,14 @@
       <c r="N282" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N278" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:O278" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
         <filter val="S"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N278">
-      <sortCondition ref="F1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A109:O274">
+      <sortCondition ref="F1:F278"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -13373,7 +13458,7 @@
       <c r="L2" s="18"/>
       <c r="M2" s="18"/>
       <c r="N2" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B2, $C$2:$C$797, C2, $D$2:$D$797, D2, $E$2:$E$797, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$797, B2, $C$2:$C$797, C2, $D$2:$D$797, D2, $E$2:$E$797, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13410,7 +13495,7 @@
       <c r="L3" s="18"/>
       <c r="M3" s="18"/>
       <c r="N3" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B3, $C$2:$C$797, C3, $D$2:$D$797, D3, $E$2:$E$797, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13447,7 +13532,7 @@
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B4, $C$2:$C$797, C4, $D$2:$D$797, D4, $E$2:$E$797, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13484,7 +13569,7 @@
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
       <c r="N5" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B5, $C$2:$C$797, C5, $D$2:$D$797, D5, $E$2:$E$797, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13521,7 +13606,7 @@
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="N6" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B6, $C$2:$C$797, C6, $D$2:$D$797, D6, $E$2:$E$797, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13560,7 +13645,7 @@
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B7, $C$2:$C$797, C7, $D$2:$D$797, D7, $E$2:$E$797, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13597,7 +13682,7 @@
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
       <c r="N8" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B8, $C$2:$C$797, C8, $D$2:$D$797, D8, $E$2:$E$797, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13636,7 +13721,7 @@
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B9, $C$2:$C$797, C9, $D$2:$D$797, D9, $E$2:$E$797, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13682,7 +13767,7 @@
         <v>250</v>
       </c>
       <c r="N10" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B10, $C$2:$C$797, C10, $D$2:$D$797, D10, $E$2:$E$797, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13719,7 +13804,7 @@
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B11, $C$2:$C$797, C11, $D$2:$D$797, D11, $E$2:$E$797, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13758,7 +13843,7 @@
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B12, $C$2:$C$797, C12, $D$2:$D$797, D12, $E$2:$E$797, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13804,7 +13889,7 @@
         <v>480</v>
       </c>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B13, $C$2:$C$797, C13, $D$2:$D$797, D13, $E$2:$E$797, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13841,7 +13926,7 @@
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
       <c r="N14" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B14, $C$2:$C$797, C14, $D$2:$D$797, D14, $E$2:$E$797, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13878,7 +13963,7 @@
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
       <c r="N15" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B15, $C$2:$C$797, C15, $D$2:$D$797, D15, $E$2:$E$797, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13924,7 +14009,7 @@
         <v>250</v>
       </c>
       <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B16, $C$2:$C$797, C16, $D$2:$D$797, D16, $E$2:$E$797, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13963,7 +14048,7 @@
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
       <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B17, $C$2:$C$797, C17, $D$2:$D$797, D17, $E$2:$E$797, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14000,7 +14085,7 @@
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
       <c r="N18" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B18, $C$2:$C$797, C18, $D$2:$D$797, D18, $E$2:$E$797, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14037,7 +14122,7 @@
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
       <c r="N19" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B19, $C$2:$C$797, C19, $D$2:$D$797, D19, $E$2:$E$797, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14074,7 +14159,7 @@
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
       <c r="N20" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B20, $C$2:$C$797, C20, $D$2:$D$797, D20, $E$2:$E$797, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14113,7 +14198,7 @@
       <c r="L21" s="18"/>
       <c r="M21" s="18"/>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B21, $C$2:$C$797, C21, $D$2:$D$797, D21, $E$2:$E$797, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14150,7 +14235,7 @@
       <c r="L22" s="18"/>
       <c r="M22" s="18"/>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B22, $C$2:$C$797, C22, $D$2:$D$797, D22, $E$2:$E$797, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14187,7 +14272,7 @@
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B23, $C$2:$C$797, C23, $D$2:$D$797, D23, $E$2:$E$797, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14224,7 +14309,7 @@
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
       <c r="N24" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B24, $C$2:$C$797, C24, $D$2:$D$797, D24, $E$2:$E$797, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14263,7 +14348,7 @@
       <c r="L25" s="18"/>
       <c r="M25" s="18"/>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B25, $C$2:$C$797, C25, $D$2:$D$797, D25, $E$2:$E$797, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14300,7 +14385,7 @@
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
       <c r="N26" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B26, $C$2:$C$797, C26, $D$2:$D$797, D26, $E$2:$E$797, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14346,7 +14431,7 @@
         <v>650</v>
       </c>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B27, $C$2:$C$797, C27, $D$2:$D$797, D27, $E$2:$E$797, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14383,7 +14468,7 @@
       <c r="L28" s="18"/>
       <c r="M28" s="18"/>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B28, $C$2:$C$797, C28, $D$2:$D$797, D28, $E$2:$E$797, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14429,7 +14514,7 @@
         <v>300</v>
       </c>
       <c r="N29" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B29, $C$2:$C$797, C29, $D$2:$D$797, D29, $E$2:$E$797, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14468,7 +14553,7 @@
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
       <c r="N30" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B30, $C$2:$C$797, C30, $D$2:$D$797, D30, $E$2:$E$797, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14505,7 +14590,7 @@
       <c r="L31" s="18"/>
       <c r="M31" s="18"/>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B31, $C$2:$C$797, C31, $D$2:$D$797, D31, $E$2:$E$797, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14542,7 +14627,7 @@
       <c r="L32" s="18"/>
       <c r="M32" s="18"/>
       <c r="N32" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B32, $C$2:$C$797, C32, $D$2:$D$797, D32, $E$2:$E$797, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14579,7 +14664,7 @@
       <c r="L33" s="18"/>
       <c r="M33" s="18"/>
       <c r="N33" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B33, $C$2:$C$797, C33, $D$2:$D$797, D33, $E$2:$E$797, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14618,7 +14703,7 @@
       <c r="L34" s="18"/>
       <c r="M34" s="18"/>
       <c r="N34" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B34, $C$2:$C$797, C34, $D$2:$D$797, D34, $E$2:$E$797, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14659,7 +14744,7 @@
       <c r="L35" s="18"/>
       <c r="M35" s="18"/>
       <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B35, $C$2:$C$797, C35, $D$2:$D$797, D35, $E$2:$E$797, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14696,7 +14781,7 @@
       <c r="L36" s="18"/>
       <c r="M36" s="18"/>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B36, $C$2:$C$797, C36, $D$2:$D$797, D36, $E$2:$E$797, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14733,7 +14818,7 @@
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
       <c r="N37" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B37, $C$2:$C$797, C37, $D$2:$D$797, D37, $E$2:$E$797, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14770,7 +14855,7 @@
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
       <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B38, $C$2:$C$797, C38, $D$2:$D$797, D38, $E$2:$E$797, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14809,7 +14894,7 @@
       <c r="L39" s="18"/>
       <c r="M39" s="18"/>
       <c r="N39" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B39, $C$2:$C$797, C39, $D$2:$D$797, D39, $E$2:$E$797, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14855,7 +14940,7 @@
         <v>940</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B40, $C$2:$C$797, C40, $D$2:$D$797, D40, $E$2:$E$797, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14892,7 +14977,7 @@
       <c r="L41" s="18"/>
       <c r="M41" s="18"/>
       <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B41, $C$2:$C$797, C41, $D$2:$D$797, D41, $E$2:$E$797, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14929,7 +15014,7 @@
       <c r="L42" s="18"/>
       <c r="M42" s="18"/>
       <c r="N42" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B42, $C$2:$C$797, C42, $D$2:$D$797, D42, $E$2:$E$797, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14966,7 +15051,7 @@
       <c r="L43" s="18"/>
       <c r="M43" s="18"/>
       <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B43, $C$2:$C$797, C43, $D$2:$D$797, D43, $E$2:$E$797, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15005,7 +15090,7 @@
       <c r="L44" s="18"/>
       <c r="M44" s="18"/>
       <c r="N44" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B44, $C$2:$C$797, C44, $D$2:$D$797, D44, $E$2:$E$797, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15046,7 +15131,7 @@
       <c r="L45" s="18"/>
       <c r="M45" s="18"/>
       <c r="N45" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B45, $C$2:$C$797, C45, $D$2:$D$797, D45, $E$2:$E$797, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15092,7 +15177,7 @@
         <v>1000</v>
       </c>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B46, $C$2:$C$797, C46, $D$2:$D$797, D46, $E$2:$E$797, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15138,7 +15223,7 @@
         <v>250</v>
       </c>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B47, $C$2:$C$797, C47, $D$2:$D$797, D47, $E$2:$E$797, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15184,7 +15269,7 @@
         <v>300</v>
       </c>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B48, $C$2:$C$797, C48, $D$2:$D$797, D48, $E$2:$E$797, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15230,7 +15315,7 @@
         <v>500</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B49, $C$2:$C$797, C49, $D$2:$D$797, D49, $E$2:$E$797, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15269,7 +15354,7 @@
       <c r="L50" s="18"/>
       <c r="M50" s="18"/>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B50, $C$2:$C$797, C50, $D$2:$D$797, D50, $E$2:$E$797, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15308,7 +15393,7 @@
       <c r="L51" s="18"/>
       <c r="M51" s="18"/>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B51, $C$2:$C$797, C51, $D$2:$D$797, D51, $E$2:$E$797, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15347,7 +15432,7 @@
       <c r="L52" s="18"/>
       <c r="M52" s="18"/>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B52, $C$2:$C$797, C52, $D$2:$D$797, D52, $E$2:$E$797, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15393,7 +15478,7 @@
         <v>275</v>
       </c>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B53, $C$2:$C$797, C53, $D$2:$D$797, D53, $E$2:$E$797, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15432,7 +15517,7 @@
       <c r="L54" s="18"/>
       <c r="M54" s="18"/>
       <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B54, $C$2:$C$797, C54, $D$2:$D$797, D54, $E$2:$E$797, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15469,7 +15554,7 @@
       <c r="L55" s="18"/>
       <c r="M55" s="18"/>
       <c r="N55" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B55, $C$2:$C$797, C55, $D$2:$D$797, D55, $E$2:$E$797, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15508,7 +15593,7 @@
       <c r="L56" s="18"/>
       <c r="M56" s="18"/>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B56, $C$2:$C$797, C56, $D$2:$D$797, D56, $E$2:$E$797, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15554,7 +15639,7 @@
         <v>300</v>
       </c>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B57, $C$2:$C$797, C57, $D$2:$D$797, D57, $E$2:$E$797, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15593,7 +15678,7 @@
       <c r="L58" s="18"/>
       <c r="M58" s="18"/>
       <c r="N58" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B58, $C$2:$C$797, C58, $D$2:$D$797, D58, $E$2:$E$797, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15629,7 +15714,7 @@
         <v>118</v>
       </c>
       <c r="N59" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B59, $C$2:$C$797, C59, $D$2:$D$797, D59, $E$2:$E$797, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15665,7 +15750,7 @@
         <v>117</v>
       </c>
       <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B60, $C$2:$C$797, C60, $D$2:$D$797, D60, $E$2:$E$797, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15699,7 +15784,7 @@
       </c>
       <c r="J61" s="21"/>
       <c r="N61" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B61, $C$2:$C$797, C61, $D$2:$D$797, D61, $E$2:$E$797, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15745,7 +15830,7 @@
         <v>285</v>
       </c>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B62, $C$2:$C$797, C62, $D$2:$D$797, D62, $E$2:$E$797, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15791,7 +15876,7 @@
         <v>726</v>
       </c>
       <c r="N63" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B63, $C$2:$C$797, C63, $D$2:$D$797, D63, $E$2:$E$797, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15825,7 +15910,7 @@
       </c>
       <c r="J64" s="21"/>
       <c r="N64" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B64, $C$2:$C$797, C64, $D$2:$D$797, D64, $E$2:$E$797, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15859,7 +15944,7 @@
       </c>
       <c r="J65" s="21"/>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B65, $C$2:$C$797, C65, $D$2:$D$797, D65, $E$2:$E$797, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15895,7 +15980,7 @@
         <v>55</v>
       </c>
       <c r="N66" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B66, $C$2:$C$797, C66, $D$2:$D$797, D66, $E$2:$E$797, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$797, B66, $C$2:$C$797, C66, $D$2:$D$797, D66, $E$2:$E$797, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -15941,7 +16026,7 @@
         <v>140</v>
       </c>
       <c r="N67" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B67, $C$2:$C$797, C67, $D$2:$D$797, D67, $E$2:$E$797, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -15987,7 +16072,7 @@
         <v>300</v>
       </c>
       <c r="N68" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B68, $C$2:$C$797, C68, $D$2:$D$797, D68, $E$2:$E$797, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -16033,7 +16118,7 @@
         <v>240</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B69, $C$2:$C$797, C69, $D$2:$D$797, D69, $E$2:$E$797, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16079,7 +16164,7 @@
         <v>300</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B70, $C$2:$C$797, C70, $D$2:$D$797, D70, $E$2:$E$797, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16125,7 +16210,7 @@
         <v>188</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B71, $C$2:$C$797, C71, $D$2:$D$797, D71, $E$2:$E$797, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16161,7 +16246,7 @@
         <v>41</v>
       </c>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B72, $C$2:$C$797, C72, $D$2:$D$797, D72, $E$2:$E$797, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16195,7 +16280,7 @@
       </c>
       <c r="J73" s="21"/>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B73, $C$2:$C$797, C73, $D$2:$D$797, D73, $E$2:$E$797, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16229,7 +16314,7 @@
       </c>
       <c r="J74" s="21"/>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B74, $C$2:$C$797, C74, $D$2:$D$797, D74, $E$2:$E$797, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16265,7 +16350,7 @@
         <v>117</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B75, $C$2:$C$797, C75, $D$2:$D$797, D75, $E$2:$E$797, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16301,7 +16386,7 @@
         <v>117</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B76, $C$2:$C$797, C76, $D$2:$D$797, D76, $E$2:$E$797, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16347,7 +16432,7 @@
         <v>320</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B77, $C$2:$C$797, C77, $D$2:$D$797, D77, $E$2:$E$797, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16393,7 +16478,7 @@
         <v>448</v>
       </c>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B78, $C$2:$C$797, C78, $D$2:$D$797, D78, $E$2:$E$797, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16427,7 +16512,7 @@
       </c>
       <c r="J79" s="21"/>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B79, $C$2:$C$797, C79, $D$2:$D$797, D79, $E$2:$E$797, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16461,7 +16546,7 @@
       </c>
       <c r="J80" s="21"/>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B80, $C$2:$C$797, C80, $D$2:$D$797, D80, $E$2:$E$797, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16507,7 +16592,7 @@
         <v>650</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B81, $C$2:$C$797, C81, $D$2:$D$797, D81, $E$2:$E$797, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16553,7 +16638,7 @@
         <v>260</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B82, $C$2:$C$797, C82, $D$2:$D$797, D82, $E$2:$E$797, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16599,7 +16684,7 @@
         <v>300</v>
       </c>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B83, $C$2:$C$797, C83, $D$2:$D$797, D83, $E$2:$E$797, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16645,7 +16730,7 @@
         <v>527.5</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B84, $C$2:$C$797, C84, $D$2:$D$797, D84, $E$2:$E$797, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16684,7 +16769,7 @@
         <v>143</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B85, $C$2:$C$797, C85, $D$2:$D$797, D85, $E$2:$E$797, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16730,7 +16815,7 @@
         <v>300</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B86, $C$2:$C$797, C86, $D$2:$D$797, D86, $E$2:$E$797, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16766,7 +16851,7 @@
         <v>118</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B87, $C$2:$C$797, C87, $D$2:$D$797, D87, $E$2:$E$797, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16800,7 +16885,7 @@
       </c>
       <c r="J88" s="21"/>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B88, $C$2:$C$797, C88, $D$2:$D$797, D88, $E$2:$E$797, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16836,7 +16921,7 @@
         <v>201</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B89, $C$2:$C$797, C89, $D$2:$D$797, D89, $E$2:$E$797, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16870,7 +16955,7 @@
       </c>
       <c r="J90" s="21"/>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B90, $C$2:$C$797, C90, $D$2:$D$797, D90, $E$2:$E$797, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16907,7 +16992,7 @@
       <c r="L91" s="18"/>
       <c r="M91" s="18"/>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B91, $C$2:$C$797, C91, $D$2:$D$797, D91, $E$2:$E$797, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16953,7 +17038,7 @@
         <v>501</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B92, $C$2:$C$797, C92, $D$2:$D$797, D92, $E$2:$E$797, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16989,7 +17074,7 @@
         <v>118</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B93, $C$2:$C$797, C93, $D$2:$D$797, D93, $E$2:$E$797, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17028,7 +17113,7 @@
         <v>145</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B94, $C$2:$C$797, C94, $D$2:$D$797, D94, $E$2:$E$797, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17067,7 +17152,7 @@
       <c r="L95" s="18"/>
       <c r="M95" s="18"/>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B95, $C$2:$C$797, C95, $D$2:$D$797, D95, $E$2:$E$797, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17113,7 +17198,7 @@
         <v>800</v>
       </c>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B96, $C$2:$C$797, C96, $D$2:$D$797, D96, $E$2:$E$797, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17149,7 +17234,7 @@
         <v>41</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B97, $C$2:$C$797, C97, $D$2:$D$797, D97, $E$2:$E$797, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17195,7 +17280,7 @@
         <v>260</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B98, $C$2:$C$797, C98, $D$2:$D$797, D98, $E$2:$E$797, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17241,7 +17326,7 @@
         <v>300</v>
       </c>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B99, $C$2:$C$797, C99, $D$2:$D$797, D99, $E$2:$E$797, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17287,7 +17372,7 @@
         <v>150</v>
       </c>
       <c r="N100" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B100, $C$2:$C$797, C100, $D$2:$D$797, D100, $E$2:$E$797, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -17333,7 +17418,7 @@
         <v>250</v>
       </c>
       <c r="N101" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B101, $C$2:$C$797, C101, $D$2:$D$797, D101, $E$2:$E$797, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -17367,7 +17452,7 @@
       </c>
       <c r="J102" s="21"/>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B102, $C$2:$C$797, C102, $D$2:$D$797, D102, $E$2:$E$797, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17403,7 +17488,7 @@
         <v>156</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B103, $C$2:$C$797, C103, $D$2:$D$797, D103, $E$2:$E$797, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17439,7 +17524,7 @@
         <v>117</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B104, $C$2:$C$797, C104, $D$2:$D$797, D104, $E$2:$E$797, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17473,7 +17558,7 @@
       </c>
       <c r="J105" s="21"/>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B105, $C$2:$C$797, C105, $D$2:$D$797, D105, $E$2:$E$797, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17519,7 +17604,7 @@
         <v>250</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B106, $C$2:$C$797, C106, $D$2:$D$797, D106, $E$2:$E$797, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17565,7 +17650,7 @@
         <v>300</v>
       </c>
       <c r="N107" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B107, $C$2:$C$797, C107, $D$2:$D$797, D107, $E$2:$E$797, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17611,7 +17696,7 @@
         <v>1800</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B108, $C$2:$C$797, C108, $D$2:$D$797, D108, $E$2:$E$797, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17657,7 +17742,7 @@
         <v>370</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B109, $C$2:$C$797, C109, $D$2:$D$797, D109, $E$2:$E$797, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17703,7 +17788,7 @@
         <v>300</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B110, $C$2:$C$797, C110, $D$2:$D$797, D110, $E$2:$E$797, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17737,7 +17822,7 @@
       </c>
       <c r="J111" s="21"/>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B111, $C$2:$C$797, C111, $D$2:$D$797, D111, $E$2:$E$797, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17783,7 +17868,7 @@
         <v>700</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B112, $C$2:$C$797, C112, $D$2:$D$797, D112, $E$2:$E$797, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17819,7 +17904,7 @@
         <v>117</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B113, $C$2:$C$797, C113, $D$2:$D$797, D113, $E$2:$E$797, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17855,7 +17940,7 @@
         <v>117</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B114, $C$2:$C$797, C114, $D$2:$D$797, D114, $E$2:$E$797, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17896,7 +17981,7 @@
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B115, $C$2:$C$797, C115, $D$2:$D$797, D115, $E$2:$E$797, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17942,7 +18027,7 @@
         <v>275</v>
       </c>
       <c r="N116" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B116, $C$2:$C$797, C116, $D$2:$D$797, D116, $E$2:$E$797, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17978,7 +18063,7 @@
         <v>118</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B117, $C$2:$C$797, C117, $D$2:$D$797, D117, $E$2:$E$797, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18020,11 +18105,11 @@
         <v>26300</v>
       </c>
       <c r="M118" s="18">
-        <f t="shared" ref="M118:M124" si="0">ABS((D118*E118)-L118)</f>
+        <f t="shared" ref="M118:M124" si="2">ABS((D118*E118)-L118)</f>
         <v>300</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B118, $C$2:$C$797, C118, $D$2:$D$797, D118, $E$2:$E$797, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18066,11 +18151,11 @@
         <v>10510</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B119, $C$2:$C$797, C119, $D$2:$D$797, D119, $E$2:$E$797, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18112,11 +18197,11 @@
         <v>5820</v>
       </c>
       <c r="M120" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B120, $C$2:$C$797, C120, $D$2:$D$797, D120, $E$2:$E$797, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18158,11 +18243,11 @@
         <v>9470</v>
       </c>
       <c r="M121" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B121, $C$2:$C$797, C121, $D$2:$D$797, D121, $E$2:$E$797, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18205,11 +18290,11 @@
         <v>5382</v>
       </c>
       <c r="M122" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>540</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B122, $C$2:$C$797, C122, $D$2:$D$797, D122, $E$2:$E$797, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18252,11 +18337,11 @@
         <v>8970</v>
       </c>
       <c r="M123" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B123, $C$2:$C$797, C123, $D$2:$D$797, D123, $E$2:$E$797, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18298,11 +18383,11 @@
         <v>33950</v>
       </c>
       <c r="M124" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>500</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B124, $C$2:$C$797, C124, $D$2:$D$797, D124, $E$2:$E$797, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18341,7 +18426,7 @@
       <c r="L125" s="18"/>
       <c r="M125" s="18"/>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B125, $C$2:$C$797, C125, $D$2:$D$797, D125, $E$2:$E$797, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18377,7 +18462,7 @@
         <v>118</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B126, $C$2:$C$797, C126, $D$2:$D$797, D126, $E$2:$E$797, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18423,7 +18508,7 @@
         <v>400</v>
       </c>
       <c r="N127" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B127, $C$2:$C$797, C127, $D$2:$D$797, D127, $E$2:$E$797, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18469,7 +18554,7 @@
         <v>300</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B128, $C$2:$C$797, C128, $D$2:$D$797, D128, $E$2:$E$797, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18515,7 +18600,7 @@
         <v>250</v>
       </c>
       <c r="N129" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B129, $C$2:$C$797, C129, $D$2:$D$797, D129, $E$2:$E$797, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18549,7 +18634,7 @@
       </c>
       <c r="J130" s="40"/>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B130, $C$2:$C$797, C130, $D$2:$D$797, D130, $E$2:$E$797, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="3">IF(COUNTIFS( $B$2:$B$797, B130, $C$2:$C$797, C130, $D$2:$D$797, D130, $E$2:$E$797, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -18591,11 +18676,11 @@
         <v>7578</v>
       </c>
       <c r="M131" s="33">
-        <f t="shared" ref="M131:M138" si="1">ABS((D131*E131)-L131)</f>
+        <f t="shared" ref="M131:M138" si="4">ABS((D131*E131)-L131)</f>
         <v>294</v>
       </c>
       <c r="N131" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B131, $C$2:$C$797, C131, $D$2:$D$797, D131, $E$2:$E$797, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -18637,11 +18722,11 @@
         <v>7578</v>
       </c>
       <c r="M132" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>294</v>
       </c>
       <c r="N132" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B132, $C$2:$C$797, C132, $D$2:$D$797, D132, $E$2:$E$797, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -18683,11 +18768,11 @@
         <v>4968</v>
       </c>
       <c r="M133" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>280</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B133, $C$2:$C$797, C133, $D$2:$D$797, D133, $E$2:$E$797, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18729,11 +18814,11 @@
         <v>15075</v>
       </c>
       <c r="M134" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>525</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B134, $C$2:$C$797, C134, $D$2:$D$797, D134, $E$2:$E$797, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18775,11 +18860,11 @@
         <v>4120</v>
       </c>
       <c r="M135" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B135, $C$2:$C$797, C135, $D$2:$D$797, D135, $E$2:$E$797, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18821,11 +18906,11 @@
         <v>4080</v>
       </c>
       <c r="M136" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B136, $C$2:$C$797, C136, $D$2:$D$797, D136, $E$2:$E$797, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18867,11 +18952,11 @@
         <v>26020</v>
       </c>
       <c r="M137" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="N137" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B137, $C$2:$C$797, C137, $D$2:$D$797, D137, $E$2:$E$797, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18913,11 +18998,11 @@
         <v>10410</v>
       </c>
       <c r="M138" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B138, $C$2:$C$797, C138, $D$2:$D$797, D138, $E$2:$E$797, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18951,7 +19036,7 @@
       </c>
       <c r="J139" s="40"/>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B139, $C$2:$C$797, C139, $D$2:$D$797, D139, $E$2:$E$797, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18993,11 +19078,11 @@
         <v>14440</v>
       </c>
       <c r="M140" s="18">
-        <f t="shared" ref="M140:M145" si="2">ABS((D140*E140)-L140)</f>
+        <f t="shared" ref="M140:M145" si="5">ABS((D140*E140)-L140)</f>
         <v>300</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B140, $C$2:$C$797, C140, $D$2:$D$797, D140, $E$2:$E$797, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19039,11 +19124,11 @@
         <v>8810</v>
       </c>
       <c r="M141" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N141" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B141, $C$2:$C$797, C141, $D$2:$D$797, D141, $E$2:$E$797, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19085,11 +19170,11 @@
         <v>16755</v>
       </c>
       <c r="M142" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>295</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B142, $C$2:$C$797, C142, $D$2:$D$797, D142, $E$2:$E$797, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19131,11 +19216,11 @@
         <v>8420</v>
       </c>
       <c r="M143" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B143, $C$2:$C$797, C143, $D$2:$D$797, D143, $E$2:$E$797, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19177,11 +19262,11 @@
         <v>25530</v>
       </c>
       <c r="M144" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N144" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B144, $C$2:$C$797, C144, $D$2:$D$797, D144, $E$2:$E$797, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19223,11 +19308,11 @@
         <v>15050</v>
       </c>
       <c r="M145" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>430</v>
       </c>
       <c r="N145" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B145, $C$2:$C$797, C145, $D$2:$D$797, D145, $E$2:$E$797, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19261,7 +19346,7 @@
       </c>
       <c r="J146" s="40"/>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B146, $C$2:$C$797, C146, $D$2:$D$797, D146, $E$2:$E$797, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19303,11 +19388,11 @@
         <v>55382.5</v>
       </c>
       <c r="M147" s="18">
-        <f t="shared" ref="M147:M153" si="3">ABS((D147*E147)-L147)</f>
+        <f t="shared" ref="M147:M153" si="6">ABS((D147*E147)-L147)</f>
         <v>1567.5</v>
       </c>
       <c r="N147" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B147, $C$2:$C$797, C147, $D$2:$D$797, D147, $E$2:$E$797, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19349,11 +19434,11 @@
         <v>32900</v>
       </c>
       <c r="M148" s="33">
+        <f t="shared" si="6"/>
+        <v>1000</v>
+      </c>
+      <c r="N148" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>1000</v>
-      </c>
-      <c r="N148" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B148, $C$2:$C$797, C148, $D$2:$D$797, D148, $E$2:$E$797, E148) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19395,11 +19480,11 @@
         <v>33200</v>
       </c>
       <c r="M149" s="33">
+        <f t="shared" si="6"/>
+        <v>700</v>
+      </c>
+      <c r="N149" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>700</v>
-      </c>
-      <c r="N149" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B149, $C$2:$C$797, C149, $D$2:$D$797, D149, $E$2:$E$797, E149) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19441,11 +19526,11 @@
         <v>25780</v>
       </c>
       <c r="M150" s="18">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
+      <c r="N150" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N150" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B150, $C$2:$C$797, C150, $D$2:$D$797, D150, $E$2:$E$797, E150) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -19487,11 +19572,11 @@
         <v>10300</v>
       </c>
       <c r="M151" s="18">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
+      <c r="N151" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>300</v>
-      </c>
-      <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B151, $C$2:$C$797, C151, $D$2:$D$797, D151, $E$2:$E$797, E151) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -19533,11 +19618,11 @@
         <v>5755</v>
       </c>
       <c r="M152" s="33">
+        <f t="shared" si="6"/>
+        <v>275</v>
+      </c>
+      <c r="N152" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>275</v>
-      </c>
-      <c r="N152" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B152, $C$2:$C$797, C152, $D$2:$D$797, D152, $E$2:$E$797, E152) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19579,11 +19664,11 @@
         <v>5805</v>
       </c>
       <c r="M153" s="33">
+        <f t="shared" si="6"/>
+        <v>225</v>
+      </c>
+      <c r="N153" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>225</v>
-      </c>
-      <c r="N153" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B153, $C$2:$C$797, C153, $D$2:$D$797, D153, $E$2:$E$797, E153) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19617,7 +19702,7 @@
       </c>
       <c r="J154" s="40"/>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B154, $C$2:$C$797, C154, $D$2:$D$797, D154, $E$2:$E$797, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19663,7 +19748,7 @@
         <v>360</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B155, $C$2:$C$797, C155, $D$2:$D$797, D155, $E$2:$E$797, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19709,7 +19794,7 @@
         <v>300</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B156, $C$2:$C$797, C156, $D$2:$D$797, D156, $E$2:$E$797, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19755,7 +19840,7 @@
         <v>500</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B157, $C$2:$C$797, C157, $D$2:$D$797, D157, $E$2:$E$797, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19801,7 +19886,7 @@
         <v>650</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B158, $C$2:$C$797, C158, $D$2:$D$797, D158, $E$2:$E$797, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19847,7 +19932,7 @@
         <v>495</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B159, $C$2:$C$797, C159, $D$2:$D$797, D159, $E$2:$E$797, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19883,7 +19968,7 @@
         <v>118</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B160, $C$2:$C$797, C160, $D$2:$D$797, D160, $E$2:$E$797, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19925,11 +20010,11 @@
         <v>20260</v>
       </c>
       <c r="M161" s="18">
-        <f t="shared" ref="M161:M166" si="4">ABS((D161*E161)-L161)</f>
+        <f t="shared" ref="M161:M166" si="7">ABS((D161*E161)-L161)</f>
         <v>300</v>
       </c>
       <c r="N161" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B161, $C$2:$C$797, C161, $D$2:$D$797, D161, $E$2:$E$797, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19971,11 +20056,11 @@
         <v>14552</v>
       </c>
       <c r="M162" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B162, $C$2:$C$797, C162, $D$2:$D$797, D162, $E$2:$E$797, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20017,11 +20102,11 @@
         <v>8220</v>
       </c>
       <c r="M163" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>360</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B163, $C$2:$C$797, C163, $D$2:$D$797, D163, $E$2:$E$797, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20063,11 +20148,11 @@
         <v>20010</v>
       </c>
       <c r="M164" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>450</v>
       </c>
       <c r="N164" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B164, $C$2:$C$797, C164, $D$2:$D$797, D164, $E$2:$E$797, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20109,11 +20194,11 @@
         <v>3560</v>
       </c>
       <c r="M165" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>175</v>
       </c>
       <c r="N165" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B165, $C$2:$C$797, C165, $D$2:$D$797, D165, $E$2:$E$797, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20155,11 +20240,11 @@
         <v>3510</v>
       </c>
       <c r="M166" s="33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>225</v>
       </c>
       <c r="N166" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B166, $C$2:$C$797, C166, $D$2:$D$797, D166, $E$2:$E$797, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20205,7 +20290,7 @@
         <v>1200</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B167, $C$2:$C$797, C167, $D$2:$D$797, D167, $E$2:$E$797, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20251,7 +20336,7 @@
         <v>300</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B168, $C$2:$C$797, C168, $D$2:$D$797, D168, $E$2:$E$797, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20290,7 +20375,7 @@
       <c r="L169" s="17"/>
       <c r="M169" s="17"/>
       <c r="N169" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B169, $C$2:$C$797, C169, $D$2:$D$797, D169, $E$2:$E$797, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20329,7 +20414,7 @@
       <c r="L170" s="17"/>
       <c r="M170" s="17"/>
       <c r="N170" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B170, $C$2:$C$797, C170, $D$2:$D$797, D170, $E$2:$E$797, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20366,7 +20451,7 @@
       <c r="L171" s="17"/>
       <c r="M171" s="17"/>
       <c r="N171" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B171, $C$2:$C$797, C171, $D$2:$D$797, D171, $E$2:$E$797, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20412,7 +20497,7 @@
         <v>450</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B172, $C$2:$C$797, C172, $D$2:$D$797, D172, $E$2:$E$797, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20449,7 +20534,7 @@
       <c r="L173" s="17"/>
       <c r="M173" s="17"/>
       <c r="N173" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B173, $C$2:$C$797, C173, $D$2:$D$797, D173, $E$2:$E$797, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20488,7 +20573,7 @@
       <c r="L174" s="17"/>
       <c r="M174" s="17"/>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B174, $C$2:$C$797, C174, $D$2:$D$797, D174, $E$2:$E$797, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20534,7 +20619,7 @@
         <v>250</v>
       </c>
       <c r="N175" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B175, $C$2:$C$797, C175, $D$2:$D$797, D175, $E$2:$E$797, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20571,7 +20656,7 @@
       <c r="L176" s="17"/>
       <c r="M176" s="17"/>
       <c r="N176" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B176, $C$2:$C$797, C176, $D$2:$D$797, D176, $E$2:$E$797, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20610,7 +20695,7 @@
       <c r="L177" s="17"/>
       <c r="M177" s="17"/>
       <c r="N177" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B177, $C$2:$C$797, C177, $D$2:$D$797, D177, $E$2:$E$797, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20649,7 +20734,7 @@
       <c r="L178" s="17"/>
       <c r="M178" s="17"/>
       <c r="N178" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B178, $C$2:$C$797, C178, $D$2:$D$797, D178, $E$2:$E$797, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20695,7 +20780,7 @@
         <v>620.99999999999636</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B179, $C$2:$C$797, C179, $D$2:$D$797, D179, $E$2:$E$797, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20741,7 +20826,7 @@
         <v>200</v>
       </c>
       <c r="N180" s="35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B180, $C$2:$C$797, C180, $D$2:$D$797, D180, $E$2:$E$797, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20778,7 +20863,7 @@
       <c r="L181" s="17"/>
       <c r="M181" s="17"/>
       <c r="N181" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B181, $C$2:$C$797, C181, $D$2:$D$797, D181, $E$2:$E$797, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20818,7 +20903,7 @@
         <v>3156</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B182, $C$2:$C$797, C182, $D$2:$D$797, D182, $E$2:$E$797, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20864,7 +20949,7 @@
         <v>500</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B183, $C$2:$C$797, C183, $D$2:$D$797, D183, $E$2:$E$797, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20901,7 +20986,7 @@
       <c r="L184" s="17"/>
       <c r="M184" s="17"/>
       <c r="N184" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B184, $C$2:$C$797, C184, $D$2:$D$797, D184, $E$2:$E$797, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20947,7 +21032,7 @@
         <v>516</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B185, $C$2:$C$797, C185, $D$2:$D$797, D185, $E$2:$E$797, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20993,7 +21078,7 @@
         <v>300</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B186, $C$2:$C$797, C186, $D$2:$D$797, D186, $E$2:$E$797, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21030,7 +21115,7 @@
       <c r="L187" s="17"/>
       <c r="M187" s="17"/>
       <c r="N187" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B187, $C$2:$C$797, C187, $D$2:$D$797, D187, $E$2:$E$797, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21076,7 +21161,7 @@
         <v>300</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B188, $C$2:$C$797, C188, $D$2:$D$797, D188, $E$2:$E$797, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21113,7 +21198,7 @@
       <c r="L189" s="17"/>
       <c r="M189" s="17"/>
       <c r="N189" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B189, $C$2:$C$797, C189, $D$2:$D$797, D189, $E$2:$E$797, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21150,7 +21235,7 @@
       <c r="L190" s="17"/>
       <c r="M190" s="17"/>
       <c r="N190" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B190, $C$2:$C$797, C190, $D$2:$D$797, D190, $E$2:$E$797, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21189,7 +21274,7 @@
       <c r="L191" s="17"/>
       <c r="M191" s="17"/>
       <c r="N191" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B191, $C$2:$C$797, C191, $D$2:$D$797, D191, $E$2:$E$797, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21226,7 +21311,7 @@
       <c r="L192" s="17"/>
       <c r="M192" s="17"/>
       <c r="N192" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B192, $C$2:$C$797, C192, $D$2:$D$797, D192, $E$2:$E$797, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21265,7 +21350,7 @@
       <c r="L193" s="17"/>
       <c r="M193" s="17"/>
       <c r="N193" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B193, $C$2:$C$797, C193, $D$2:$D$797, D193, $E$2:$E$797, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21302,7 +21387,7 @@
       <c r="L194" s="17"/>
       <c r="M194" s="17"/>
       <c r="N194" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B194, $C$2:$C$797, C194, $D$2:$D$797, D194, $E$2:$E$797, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="8">IF(COUNTIFS( $B$2:$B$797, B194, $C$2:$C$797, C194, $D$2:$D$797, D194, $E$2:$E$797, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -21339,7 +21424,7 @@
       <c r="L195" s="17"/>
       <c r="M195" s="17"/>
       <c r="N195" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B195, $C$2:$C$797, C195, $D$2:$D$797, D195, $E$2:$E$797, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21376,7 +21461,7 @@
       <c r="L196" s="17"/>
       <c r="M196" s="17"/>
       <c r="N196" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B196, $C$2:$C$797, C196, $D$2:$D$797, D196, $E$2:$E$797, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21413,7 +21498,7 @@
       <c r="L197" s="17"/>
       <c r="M197" s="17"/>
       <c r="N197" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B197, $C$2:$C$797, C197, $D$2:$D$797, D197, $E$2:$E$797, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21452,7 +21537,7 @@
       <c r="L198" s="17"/>
       <c r="M198" s="17"/>
       <c r="N198" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B198, $C$2:$C$797, C198, $D$2:$D$797, D198, $E$2:$E$797, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21489,7 +21574,7 @@
       <c r="L199" s="17"/>
       <c r="M199" s="17"/>
       <c r="N199" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B199, $C$2:$C$797, C199, $D$2:$D$797, D199, $E$2:$E$797, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21535,7 +21620,7 @@
         <v>300</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B200, $C$2:$C$797, C200, $D$2:$D$797, D200, $E$2:$E$797, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21572,7 +21657,7 @@
       <c r="L201" s="17"/>
       <c r="M201" s="17"/>
       <c r="N201" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B201, $C$2:$C$797, C201, $D$2:$D$797, D201, $E$2:$E$797, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21609,7 +21694,7 @@
       <c r="L202" s="17"/>
       <c r="M202" s="17"/>
       <c r="N202" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B202, $C$2:$C$797, C202, $D$2:$D$797, D202, $E$2:$E$797, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21648,7 +21733,7 @@
       <c r="L203" s="17"/>
       <c r="M203" s="17"/>
       <c r="N203" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B203, $C$2:$C$797, C203, $D$2:$D$797, D203, $E$2:$E$797, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21685,7 +21770,7 @@
       <c r="L204" s="17"/>
       <c r="M204" s="17"/>
       <c r="N204" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B204, $C$2:$C$797, C204, $D$2:$D$797, D204, $E$2:$E$797, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21722,7 +21807,7 @@
       <c r="L205" s="17"/>
       <c r="M205" s="17"/>
       <c r="N205" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B205, $C$2:$C$797, C205, $D$2:$D$797, D205, $E$2:$E$797, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21768,7 +21853,7 @@
         <v>300</v>
       </c>
       <c r="N206" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B206, $C$2:$C$797, C206, $D$2:$D$797, D206, $E$2:$E$797, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21805,7 +21890,7 @@
       <c r="L207" s="17"/>
       <c r="M207" s="17"/>
       <c r="N207" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B207, $C$2:$C$797, C207, $D$2:$D$797, D207, $E$2:$E$797, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21842,7 +21927,7 @@
       <c r="L208" s="17"/>
       <c r="M208" s="17"/>
       <c r="N208" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B208, $C$2:$C$797, C208, $D$2:$D$797, D208, $E$2:$E$797, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21879,7 +21964,7 @@
       <c r="L209" s="17"/>
       <c r="M209" s="17"/>
       <c r="N209" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B209, $C$2:$C$797, C209, $D$2:$D$797, D209, $E$2:$E$797, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21925,7 +22010,7 @@
         <v>222.75</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B210, $C$2:$C$797, C210, $D$2:$D$797, D210, $E$2:$E$797, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21964,7 +22049,7 @@
       <c r="L211" s="17"/>
       <c r="M211" s="17"/>
       <c r="N211" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B211, $C$2:$C$797, C211, $D$2:$D$797, D211, $E$2:$E$797, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22003,7 +22088,7 @@
       <c r="L212" s="17"/>
       <c r="M212" s="17"/>
       <c r="N212" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B212, $C$2:$C$797, C212, $D$2:$D$797, D212, $E$2:$E$797, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22049,7 +22134,7 @@
         <v>300</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B213, $C$2:$C$797, C213, $D$2:$D$797, D213, $E$2:$E$797, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22086,7 +22171,7 @@
       <c r="L214" s="17"/>
       <c r="M214" s="17"/>
       <c r="N214" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B214, $C$2:$C$797, C214, $D$2:$D$797, D214, $E$2:$E$797, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22125,7 +22210,7 @@
       <c r="L215" s="17"/>
       <c r="M215" s="17"/>
       <c r="N215" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B215, $C$2:$C$797, C215, $D$2:$D$797, D215, $E$2:$E$797, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22164,7 +22249,7 @@
       <c r="L216" s="17"/>
       <c r="M216" s="17"/>
       <c r="N216" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B216, $C$2:$C$797, C216, $D$2:$D$797, D216, $E$2:$E$797, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22201,7 +22286,7 @@
       <c r="L217" s="17"/>
       <c r="M217" s="17"/>
       <c r="N217" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B217, $C$2:$C$797, C217, $D$2:$D$797, D217, $E$2:$E$797, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22238,7 +22323,7 @@
       <c r="L218" s="17"/>
       <c r="M218" s="17"/>
       <c r="N218" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B218, $C$2:$C$797, C218, $D$2:$D$797, D218, $E$2:$E$797, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22275,7 +22360,7 @@
       <c r="L219" s="17"/>
       <c r="M219" s="17"/>
       <c r="N219" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B219, $C$2:$C$797, C219, $D$2:$D$797, D219, $E$2:$E$797, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22312,7 +22397,7 @@
       <c r="L220" s="17"/>
       <c r="M220" s="17"/>
       <c r="N220" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B220, $C$2:$C$797, C220, $D$2:$D$797, D220, $E$2:$E$797, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22349,7 +22434,7 @@
       <c r="L221" s="17"/>
       <c r="M221" s="17"/>
       <c r="N221" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B221, $C$2:$C$797, C221, $D$2:$D$797, D221, $E$2:$E$797, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22388,7 +22473,7 @@
       <c r="L222" s="17"/>
       <c r="M222" s="17"/>
       <c r="N222" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B222, $C$2:$C$797, C222, $D$2:$D$797, D222, $E$2:$E$797, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22425,7 +22510,7 @@
       <c r="L223" s="17"/>
       <c r="M223" s="17"/>
       <c r="N223" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B223, $C$2:$C$797, C223, $D$2:$D$797, D223, $E$2:$E$797, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22464,7 +22549,7 @@
       <c r="L224" s="17"/>
       <c r="M224" s="17"/>
       <c r="N224" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B224, $C$2:$C$797, C224, $D$2:$D$797, D224, $E$2:$E$797, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22503,7 +22588,7 @@
       <c r="L225" s="17"/>
       <c r="M225" s="17"/>
       <c r="N225" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B225, $C$2:$C$797, C225, $D$2:$D$797, D225, $E$2:$E$797, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22549,7 +22634,7 @@
         <v>300</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B226, $C$2:$C$797, C226, $D$2:$D$797, D226, $E$2:$E$797, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22588,7 +22673,7 @@
       <c r="L227" s="17"/>
       <c r="M227" s="17"/>
       <c r="N227" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B227, $C$2:$C$797, C227, $D$2:$D$797, D227, $E$2:$E$797, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22625,7 +22710,7 @@
       <c r="L228" s="17"/>
       <c r="M228" s="17"/>
       <c r="N228" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B228, $C$2:$C$797, C228, $D$2:$D$797, D228, $E$2:$E$797, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22662,7 +22747,7 @@
       <c r="L229" s="17"/>
       <c r="M229" s="17"/>
       <c r="N229" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B229, $C$2:$C$797, C229, $D$2:$D$797, D229, $E$2:$E$797, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22699,7 +22784,7 @@
       <c r="L230" s="17"/>
       <c r="M230" s="17"/>
       <c r="N230" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B230, $C$2:$C$797, C230, $D$2:$D$797, D230, $E$2:$E$797, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22738,7 +22823,7 @@
       <c r="L231" s="17"/>
       <c r="M231" s="17"/>
       <c r="N231" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B231, $C$2:$C$797, C231, $D$2:$D$797, D231, $E$2:$E$797, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22777,7 +22862,7 @@
       <c r="L232" s="17"/>
       <c r="M232" s="17"/>
       <c r="N232" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B232, $C$2:$C$797, C232, $D$2:$D$797, D232, $E$2:$E$797, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22816,7 +22901,7 @@
       <c r="L233" s="17"/>
       <c r="M233" s="17"/>
       <c r="N233" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B233, $C$2:$C$797, C233, $D$2:$D$797, D233, $E$2:$E$797, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22853,7 +22938,7 @@
       <c r="L234" s="17"/>
       <c r="M234" s="17"/>
       <c r="N234" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B234, $C$2:$C$797, C234, $D$2:$D$797, D234, $E$2:$E$797, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22890,7 +22975,7 @@
       <c r="L235" s="17"/>
       <c r="M235" s="17"/>
       <c r="N235" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B235, $C$2:$C$797, C235, $D$2:$D$797, D235, $E$2:$E$797, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22936,7 +23021,7 @@
         <v>300</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B236, $C$2:$C$797, C236, $D$2:$D$797, D236, $E$2:$E$797, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22973,7 +23058,7 @@
       <c r="L237" s="17"/>
       <c r="M237" s="17"/>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B237, $C$2:$C$797, C237, $D$2:$D$797, D237, $E$2:$E$797, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23010,7 +23095,7 @@
       <c r="L238" s="17"/>
       <c r="M238" s="17"/>
       <c r="N238" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B238, $C$2:$C$797, C238, $D$2:$D$797, D238, $E$2:$E$797, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23049,7 +23134,7 @@
       <c r="L239" s="17"/>
       <c r="M239" s="17"/>
       <c r="N239" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B239, $C$2:$C$797, C239, $D$2:$D$797, D239, $E$2:$E$797, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23088,7 +23173,7 @@
       <c r="L240" s="17"/>
       <c r="M240" s="17"/>
       <c r="N240" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B240, $C$2:$C$797, C240, $D$2:$D$797, D240, $E$2:$E$797, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23125,7 +23210,7 @@
       <c r="L241" s="17"/>
       <c r="M241" s="17"/>
       <c r="N241" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B241, $C$2:$C$797, C241, $D$2:$D$797, D241, $E$2:$E$797, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23162,7 +23247,7 @@
       <c r="L242" s="17"/>
       <c r="M242" s="17"/>
       <c r="N242" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B242, $C$2:$C$797, C242, $D$2:$D$797, D242, $E$2:$E$797, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23208,7 +23293,7 @@
         <v>442</v>
       </c>
       <c r="N243" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B243, $C$2:$C$797, C243, $D$2:$D$797, D243, $E$2:$E$797, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23245,7 +23330,7 @@
       <c r="L244" s="17"/>
       <c r="M244" s="17"/>
       <c r="N244" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B244, $C$2:$C$797, C244, $D$2:$D$797, D244, $E$2:$E$797, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23282,7 +23367,7 @@
       <c r="L245" s="17"/>
       <c r="M245" s="17"/>
       <c r="N245" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B245, $C$2:$C$797, C245, $D$2:$D$797, D245, $E$2:$E$797, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23323,7 +23408,7 @@
       <c r="L246" s="17"/>
       <c r="M246" s="17"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B246, $C$2:$C$797, C246, $D$2:$D$797, D246, $E$2:$E$797, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23360,7 +23445,7 @@
       <c r="L247" s="17"/>
       <c r="M247" s="17"/>
       <c r="N247" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B247, $C$2:$C$797, C247, $D$2:$D$797, D247, $E$2:$E$797, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23397,7 +23482,7 @@
       <c r="L248" s="17"/>
       <c r="M248" s="17"/>
       <c r="N248" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B248, $C$2:$C$797, C248, $D$2:$D$797, D248, $E$2:$E$797, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23434,7 +23519,7 @@
       <c r="L249" s="17"/>
       <c r="M249" s="17"/>
       <c r="N249" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B249, $C$2:$C$797, C249, $D$2:$D$797, D249, $E$2:$E$797, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23471,7 +23556,7 @@
       <c r="L250" s="17"/>
       <c r="M250" s="17"/>
       <c r="N250" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B250, $C$2:$C$797, C250, $D$2:$D$797, D250, $E$2:$E$797, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23510,7 +23595,7 @@
       <c r="L251" s="17"/>
       <c r="M251" s="17"/>
       <c r="N251" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B251, $C$2:$C$797, C251, $D$2:$D$797, D251, $E$2:$E$797, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23547,7 +23632,7 @@
       <c r="L252" s="17"/>
       <c r="M252" s="17"/>
       <c r="N252" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B252, $C$2:$C$797, C252, $D$2:$D$797, D252, $E$2:$E$797, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23584,7 +23669,7 @@
       <c r="L253" s="17"/>
       <c r="M253" s="17"/>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B253, $C$2:$C$797, C253, $D$2:$D$797, D253, $E$2:$E$797, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23623,7 +23708,7 @@
       <c r="L254" s="17"/>
       <c r="M254" s="17"/>
       <c r="N254" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B254, $C$2:$C$797, C254, $D$2:$D$797, D254, $E$2:$E$797, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23660,7 +23745,7 @@
       <c r="L255" s="17"/>
       <c r="M255" s="17"/>
       <c r="N255" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B255, $C$2:$C$797, C255, $D$2:$D$797, D255, $E$2:$E$797, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23697,7 +23782,7 @@
       <c r="L256" s="17"/>
       <c r="M256" s="17"/>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B256, $C$2:$C$797, C256, $D$2:$D$797, D256, $E$2:$E$797, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23734,7 +23819,7 @@
       <c r="L257" s="17"/>
       <c r="M257" s="17"/>
       <c r="N257" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B257, $C$2:$C$797, C257, $D$2:$D$797, D257, $E$2:$E$797, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23771,7 +23856,7 @@
       <c r="L258" s="17"/>
       <c r="M258" s="17"/>
       <c r="N258" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B258, $C$2:$C$797, C258, $D$2:$D$797, D258, $E$2:$E$797, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N278" si="9">IF(COUNTIFS( $B$2:$B$797, B258, $C$2:$C$797, C258, $D$2:$D$797, D258, $E$2:$E$797, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -23808,7 +23893,7 @@
       <c r="L259" s="17"/>
       <c r="M259" s="17"/>
       <c r="N259" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B259, $C$2:$C$797, C259, $D$2:$D$797, D259, $E$2:$E$797, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23845,7 +23930,7 @@
       <c r="L260" s="17"/>
       <c r="M260" s="17"/>
       <c r="N260" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B260, $C$2:$C$797, C260, $D$2:$D$797, D260, $E$2:$E$797, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23884,7 +23969,7 @@
       <c r="L261" s="17"/>
       <c r="M261" s="17"/>
       <c r="N261" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B261, $C$2:$C$797, C261, $D$2:$D$797, D261, $E$2:$E$797, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23921,7 +24006,7 @@
       <c r="L262" s="17"/>
       <c r="M262" s="17"/>
       <c r="N262" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B262, $C$2:$C$797, C262, $D$2:$D$797, D262, $E$2:$E$797, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23958,7 +24043,7 @@
       <c r="L263" s="17"/>
       <c r="M263" s="17"/>
       <c r="N263" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B263, $C$2:$C$797, C263, $D$2:$D$797, D263, $E$2:$E$797, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23995,7 +24080,7 @@
       <c r="L264" s="17"/>
       <c r="M264" s="17"/>
       <c r="N264" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B264, $C$2:$C$797, C264, $D$2:$D$797, D264, $E$2:$E$797, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24032,7 +24117,7 @@
       <c r="L265" s="17"/>
       <c r="M265" s="17"/>
       <c r="N265" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B265, $C$2:$C$797, C265, $D$2:$D$797, D265, $E$2:$E$797, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24069,7 +24154,7 @@
       <c r="L266" s="17"/>
       <c r="M266" s="17"/>
       <c r="N266" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B266, $C$2:$C$797, C266, $D$2:$D$797, D266, $E$2:$E$797, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24108,7 +24193,7 @@
       <c r="L267" s="17"/>
       <c r="M267" s="17"/>
       <c r="N267" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B267, $C$2:$C$797, C267, $D$2:$D$797, D267, $E$2:$E$797, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24143,7 +24228,7 @@
         <v>300.00000000000182</v>
       </c>
       <c r="N268" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B268, $C$2:$C$797, C268, $D$2:$D$797, D268, $E$2:$E$797, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24174,11 +24259,11 @@
         <v>5180</v>
       </c>
       <c r="M269" s="27">
-        <f t="shared" ref="M269:M278" si="5">ABS((D269*E269)-L269)</f>
+        <f t="shared" ref="M269:M278" si="10">ABS((D269*E269)-L269)</f>
         <v>268</v>
       </c>
       <c r="N269" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B269, $C$2:$C$797, C269, $D$2:$D$797, D269, $E$2:$E$797, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24209,11 +24294,11 @@
         <v>18140</v>
       </c>
       <c r="M270" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>650</v>
       </c>
       <c r="N270" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B270, $C$2:$C$797, C270, $D$2:$D$797, D270, $E$2:$E$797, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24245,11 +24330,11 @@
         <v>9345</v>
       </c>
       <c r="M271" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>525</v>
       </c>
       <c r="N271" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B271, $C$2:$C$797, C271, $D$2:$D$797, D271, $E$2:$E$797, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24280,11 +24365,11 @@
         <v>8480</v>
       </c>
       <c r="M272" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>280</v>
       </c>
       <c r="N272" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B272, $C$2:$C$797, C272, $D$2:$D$797, D272, $E$2:$E$797, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24315,11 +24400,11 @@
         <v>2105</v>
       </c>
       <c r="M273" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>250</v>
       </c>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B273, $C$2:$C$797, C273, $D$2:$D$797, D273, $E$2:$E$797, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24350,11 +24435,11 @@
         <v>9220</v>
       </c>
       <c r="M274" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>650</v>
       </c>
       <c r="N274" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B274, $C$2:$C$797, C274, $D$2:$D$797, D274, $E$2:$E$797, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24385,11 +24470,11 @@
         <v>6880</v>
       </c>
       <c r="M275" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>460</v>
       </c>
       <c r="N275" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B275, $C$2:$C$797, C275, $D$2:$D$797, D275, $E$2:$E$797, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24420,11 +24505,11 @@
         <v>9000</v>
       </c>
       <c r="M276" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
       <c r="N276" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B276, $C$2:$C$797, C276, $D$2:$D$797, D276, $E$2:$E$797, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24455,11 +24540,11 @@
         <v>9470</v>
       </c>
       <c r="M277" s="33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
       <c r="N277" s="34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B277, $C$2:$C$797, C277, $D$2:$D$797, D277, $E$2:$E$797, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -24488,11 +24573,11 @@
         <v>12800</v>
       </c>
       <c r="M278" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>290</v>
       </c>
       <c r="N278" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$797, B278, $C$2:$C$797, C278, $D$2:$D$797, D278, $E$2:$E$797, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
